--- a/knowledge/exhibits/Boise_Deals_Normalized_Underwriting_v2.xlsx
+++ b/knowledge/exhibits/Boise_Deals_Normalized_Underwriting_v2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="403">
   <si>
     <t xml:space="preserve">Boise MSA — Deal Comparison &amp; Developer Underwriting Normalization (v2)</t>
   </si>
@@ -619,7 +619,7 @@
     <t xml:space="preserve">Untrended taxes embedded ($, est)</t>
   </si>
   <si>
-    <t xml:space="preserve">2031 taxes deflated 3%/yr</t>
+    <t xml:space="preserve">2031 taxes deflated 3%/yr; consistent with their cost-basis assessment path (~$73.5M 2026-equiv x 0.45%)</t>
   </si>
   <si>
     <t xml:space="preserve">Sale F12 NOI ($, Jan-30)</t>
@@ -773,6 +773,51 @@
   </si>
   <si>
     <t xml:space="preserve">  @ alt cap</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D. TAX METHODOLOGY — VERIFIED, THEIRS vs OURS (apples-to-apples)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THEIR ENGINE (Tax Calcs tab): assessment = cumulative construction cost; steps to $80.3M at completion (2030), +3%/yr to ~$82.7-85.4M in 2031 = ~83% of their own $102.5M sale. Taxed at 0.45%. Construction-period taxes capitalized (fine). NO step-up to value at stabilization and NO reassessment for the buyer at sale.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OUR ENGINE (Seasons Taxes tab): current assessment $92.99M = 78.8% of our price; reassessment year 2027 steps taxable value to 95% x purchase price ($112.1M); +3.5%/yr assessment, -2%/yr levy; exit F12 NOI trued up to buyer taxes at 95% x EXIT price (= the -$15,345 adj in Assumptions M38).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emblem 2031 taxes as modeled ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A-OperBgt col H; = $1,501/u; implied assessment $85.4M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Emblem 2031 NOI-ex-tax ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMG-convention value @ C34 cap ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">closed-form: V = NOI-ex-tax / (cap + 0.95 x levy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMG-convention 2031 taxes ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs $1,501/u as modeled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Understatement ($/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~8-11bp of stabilized YoC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capitalized impact on exit value ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~1.0-1.5% of their gross sale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SYMMETRY NOTE: Seasons current assessment (79% of price) shows the same assessor lag Emblem banks on — but TMG conservatively steps to 95% within a year on BOTH sides of the trade. If you underwrote Seasons on Emblem-style lag, Y1 taxes would be ~$419K not $482K (+5bp on the Y1 cap). The convention difference, not the levy, is the entire dispute.</t>
   </si>
   <si>
     <t xml:space="preserve">The Judy (Hawkins) — Normalization Detail</t>
@@ -1873,84 +1918,84 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="34" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="34" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="34" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="34" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="34" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="34" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>380</v>
+        <v>395</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="34" t="s">
-        <v>381</v>
+        <v>396</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>382</v>
+        <v>397</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="34" t="s">
-        <v>383</v>
+        <v>398</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>384</v>
+        <v>399</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="34" t="s">
-        <v>385</v>
+        <v>400</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>386</v>
+        <v>401</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="s">
-        <v>387</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>
@@ -3969,7 +4014,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F51"/>
+  <dimension ref="B2:F68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -4061,7 +4106,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
         <v>195</v>
       </c>
@@ -4450,7 +4495,147 @@
       </c>
       <c r="F51" s="2"/>
     </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B55" s="16" t="s">
+        <v>249</v>
+      </c>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+    </row>
+    <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B56" s="16" t="s">
+        <v>250</v>
+      </c>
+      <c r="C56" s="16"/>
+      <c r="D56" s="16"/>
+      <c r="E56" s="16"/>
+      <c r="F56" s="16"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="C57" s="9" t="n">
+        <v>384319</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="13" t="s">
+        <v>253</v>
+      </c>
+      <c r="C58" s="10" t="n">
+        <f aca="false">5825182+C57</f>
+        <v>6209501</v>
+      </c>
+      <c r="F58" s="2"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="C59" s="10" t="n">
+        <f aca="false">C58/(C34+C33)</f>
+        <v>109370339.057684</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="13" t="s">
+        <v>256</v>
+      </c>
+      <c r="C60" s="10" t="n">
+        <f aca="false">C33*C59</f>
+        <v>467558.199471598</v>
+      </c>
+      <c r="F60" s="2"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C61" s="10" t="n">
+        <f aca="false">C60/C8</f>
+        <v>1826.39921668593</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="C62" s="10" t="n">
+        <f aca="false">C60-C57</f>
+        <v>83239.1994715983</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="C63" s="10" t="n">
+        <f aca="false">C62/C34</f>
+        <v>1585508.56136378</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="C64" s="10" t="n">
+        <f aca="false">C63/C8</f>
+        <v>6193.39281782726</v>
+      </c>
+      <c r="F64" s="2"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B66" s="16" t="s">
+        <v>262</v>
+      </c>
+      <c r="C66" s="16"/>
+      <c r="D66" s="16"/>
+      <c r="E66" s="16"/>
+      <c r="F66" s="16"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="16"/>
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="16"/>
+      <c r="C68" s="16"/>
+      <c r="D68" s="16"/>
+      <c r="E68" s="16"/>
+      <c r="F68" s="16"/>
+    </row>
   </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="B55:F55"/>
+    <mergeCell ref="B56:F56"/>
+    <mergeCell ref="B66:F68"/>
+  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4477,12 +4662,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4528,7 +4713,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>250</v>
+        <v>265</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C9*C6</f>
@@ -4538,7 +4723,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>251</v>
+        <v>266</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2914298</v>
@@ -4547,41 +4732,41 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>252</v>
+        <v>267</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>356965</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>253</v>
+        <v>268</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">C12/1.03^3</f>
         <v>326673.542431001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>255</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>256</v>
+        <v>271</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>578083</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>257</v>
+        <v>272</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>258</v>
+        <v>273</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>3075765</v>
@@ -4606,23 +4791,23 @@
         <v>58586000</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>259</v>
+        <v>274</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>2448783</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>261</v>
+        <v>276</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>262</v>
+        <v>277</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>6.13</v>
@@ -4631,7 +4816,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>263</v>
+        <v>278</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4642,7 +4827,7 @@
         <v>3000</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4657,13 +4842,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="C24" s="11" t="n">
         <v>0.0092</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4687,24 +4872,24 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>0.0525</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="C28" s="26" t="n">
         <v>625000</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4714,19 +4899,19 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">C10+C13+C23*0.9413</f>
         <v>2958295.893331</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="13" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">C31/(C27+C26)</f>
@@ -4736,7 +4921,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C33" s="10" t="n">
         <f aca="false">C26*C32</f>
@@ -4753,7 +4938,7 @@
         <v>2606.17063281815</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4768,14 +4953,14 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
       <c r="C36" s="21" t="n">
         <f aca="false">C35/C6</f>
         <v>0.0608297357759334</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4787,12 +4972,12 @@
         <v>3354160.940263</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">C37/(C27+C26)</f>
@@ -4809,17 +4994,17 @@
         <v>338091.070576703</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="14" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="13" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">C28*C19</f>
@@ -4829,7 +5014,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="13" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">C41-C18</f>
@@ -4839,7 +5024,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="13" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">C6+C42</f>
@@ -4849,14 +5034,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
       <c r="C44" s="21" t="n">
         <f aca="false">C35/C43</f>
         <v>0.0588774039935301</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
     </row>
   </sheetData>
@@ -4886,22 +5071,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="29" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4946,7 +5131,7 @@
         <v>0.0720729413872807</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5051,7 +5236,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="14" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5096,7 +5281,7 @@
         <v>2.21140419805461</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5226,24 +5411,24 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="14" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="C25" s="7" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5271,7 +5456,7 @@
         <v>0.0600840809502929</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5376,7 +5561,7 @@
     </row>
     <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
   </sheetData>
@@ -5406,31 +5591,31 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="C6" s="31" t="n">
         <v>0.004053</v>
@@ -5439,12 +5624,12 @@
         <v>0.002033</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C7" s="31" t="n">
         <v>0.002797</v>
@@ -5453,12 +5638,12 @@
         <v>0.000332</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="C8" s="31" t="n">
         <v>0.002209</v>
@@ -5467,12 +5652,12 @@
         <v>0.002142</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="C9" s="31" t="n">
         <v>0.009059</v>
@@ -5481,17 +5666,17 @@
         <v>0.004507</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="14" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="32" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="C12" s="32"/>
       <c r="D12" s="32"/>
@@ -5514,36 +5699,36 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="14" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">3428-1340</f>
         <v>2088</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="C18" s="10" t="n">
         <f aca="false">C17/0.05</f>
         <v>41760</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>381944</v>
@@ -5552,19 +5737,19 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="C20" s="10" t="n">
         <f aca="false">5027967+C17*288</f>
         <v>5629311</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">C20/0.045709/288</f>
@@ -5574,7 +5759,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="C22" s="9" t="n">
         <v>327778</v>
@@ -5583,31 +5768,31 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="C23" s="15" t="n">
         <f aca="false">C22/C21-1</f>
         <v>-0.233488338914656</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="C24" s="10" t="n">
         <f aca="false">(5904654-C17*360)/0.05/360</f>
         <v>286276.333333333</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="16" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="C26" s="16"/>
       <c r="D26" s="16"/>
@@ -5652,12 +5837,12 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5671,7 +5856,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="6" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="C6" s="8" t="n">
         <v>1130</v>
@@ -5682,7 +5867,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="6" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="C7" s="8" t="n">
         <v>228</v>
@@ -5693,7 +5878,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="6" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>507</v>
@@ -5704,7 +5889,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>309</v>
@@ -5715,78 +5900,78 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="14" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>43</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="C13" s="8" t="n">
         <v>552</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="C14" s="8" t="n">
         <v>213</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="C15" s="8" t="n">
         <v>212</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="C16" s="8" t="n">
         <v>164</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="C17" s="8" t="n">
         <v>72</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="17" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="C18" s="33" t="n">
         <f aca="false">SUM(C13:C17)</f>
@@ -5795,12 +5980,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="14" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>43</v>
@@ -5808,7 +5993,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="C22" s="8" t="n">
         <v>472</v>
@@ -5816,7 +6001,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="C23" s="8" t="n">
         <v>390</v>
@@ -5824,7 +6009,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="C24" s="8" t="n">
         <v>322</v>
@@ -5832,7 +6017,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="C25" s="8" t="n">
         <v>301</v>
@@ -5840,7 +6025,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="C26" s="8" t="n">
         <v>275</v>
@@ -5848,7 +6033,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="C27" s="8" t="n">
         <v>270</v>
@@ -5856,7 +6041,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="C28" s="8" t="n">
         <v>250</v>
@@ -5864,7 +6049,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="C29" s="8" t="n">
         <v>200</v>
@@ -5872,7 +6057,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="13" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="C30" s="8" t="n">
         <v>200</v>
@@ -5880,7 +6065,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="C31" s="8" t="n">
         <v>162</v>
@@ -5888,7 +6073,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="13" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="C32" s="8" t="n">
         <v>156</v>
@@ -5896,7 +6081,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="C33" s="8" t="n">
         <v>138</v>
@@ -5904,7 +6089,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="13" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="C34" s="8" t="n">
         <v>36</v>
@@ -5912,7 +6097,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="C35" s="8" t="n">
         <v>256</v>
@@ -5920,7 +6105,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="17" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="C36" s="33" t="n">
         <f aca="false">SUM(C22:C35)</f>
@@ -5929,7 +6114,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B38" s="16" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="C38" s="16"/>
       <c r="D38" s="16"/>

--- a/knowledge/exhibits/Boise_Deals_Normalized_Underwriting_v2.xlsx
+++ b/knowledge/exhibits/Boise_Deals_Normalized_Underwriting_v2.xlsx
@@ -11,13 +11,14 @@
     <sheet name="README" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="1_Deals" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="2_ProFormas" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="3_Dev_Feasibility" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="4_Emblem_Norm" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="5_Judy_Norm" sheetId="6" state="visible" r:id="rId8"/>
-    <sheet name="6_Sensitivities" sheetId="7" state="visible" r:id="rId9"/>
-    <sheet name="7_Taxes" sheetId="8" state="visible" r:id="rId10"/>
-    <sheet name="8_Supply" sheetId="9" state="visible" r:id="rId11"/>
-    <sheet name="9_Sources" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="2b_Prelude_Actuals" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="3_Dev_Feasibility" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="4_Emblem_Norm" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="5_Judy_Norm" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="6_Sensitivities" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="7_Taxes" sheetId="9" state="visible" r:id="rId11"/>
+    <sheet name="8_Supply" sheetId="10" state="visible" r:id="rId12"/>
+    <sheet name="9_Sources" sheetId="11" state="visible" r:id="rId13"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="403">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="454">
   <si>
     <t xml:space="preserve">Boise MSA — Deal Comparison &amp; Developer Underwriting Normalization (v2)</t>
   </si>
@@ -385,6 +386,162 @@
     <t xml:space="preserve">Prelude reconciliation: EGI $20,862 (Rev&amp;Exp H27/280) − opex $6,536 = NOI $14,326 ≈ $14,335 (H53/280; rounding). Old-model note: its "Total Controllable" excludes utilities; utilities+insurance+mgmt+taxes reconcile to total.</t>
   </si>
   <si>
+    <t xml:space="preserve">Prelude at Paramount — ACTUALS vs Acquisition Underwrite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sources: 12-month accrual statement Aug-25 to Jul-26 (7 true months post-close: Jan-Jul 2026) and Rent Roll w/ Lease Charges 8/13/2026. UW = our Dec-2025 acquisition model Y1. The first live test of the Meridian recovery thesis.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$/unit/yr unless noted</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UW Y1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual 7-mo ann.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Actual T3 ann. (May-Jul)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3 vs UW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">REVENUE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gross potential rent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM market-rent line held flat at $1,723.50/unit all 7 months</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loss to lease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Shrinking monthly: Jan -3.2% of GPR to Jul -2.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concessions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RED FLAG: T3 pace 5.7% of potential rent vs 2.5% UW; one-time (upfront) concessions on new signings</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vacancy + employee units</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Economic vacancy ~11% Jan-Apr to 6.1% T3 - strong absorption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Net rental income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other income</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gap = bulk internet UW income not yet implemented ($0 actual); garages $609 actual vs $759 UW</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OPEX</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Payroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Favorable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">G&amp;A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Turnover / make-ready / amenities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contracts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4% of EGI actual</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RE taxes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Accruing exactly at the UW 2026 bill ($333.5K) - consistent with the 95% reassessment step</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~$500/u favorable, led by payroll</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T3 -3.9% vs UW Y1 - behind but converging as vacancy burns off</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RENT ROLL 8/13/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Units paying rent (of 280)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.8% - 9 units down/model/vacant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In-place base rent ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vs UW Y1 rent/occupied $1,668: +0.7% AHEAD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PM market rent ($/mo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">UW Y1 avg market rent $1,730</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New leases May-Aug 2026 ($/mo, n=56)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ON TARGET vs UW Y1 market rent - face rents; ~5-6% one-time concessions apply</t>
+  </si>
+  <si>
+    <t xml:space="preserve">New leases Jan-Apr 2026 ($/mo, n=28)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Winter signings were weak; intra-2026 acceleration is real</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NEW-LEASE COHORTS BY FLOOR PLAN ($/mo) — col D = Jan-Apr 2026 cohort, col E = May-Aug 2026 cohort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  1BR 787sf (pprA1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jan-Apr n=15 / May-Aug n=20: +10.5% cohort-over-cohort</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2BR 1092sf (pprB1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n=4 / n=22: +5.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  2BR 1172sf (pprB2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n=4 / n=10: +4.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  3BR 1291sf (pprC1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n=5 / n=4: +12.4% (small n)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VERDICT: The recovery thesis is tracking. Occupancy recovered 11% to 6% economic vacancy in six months; recent new leases sign at the UW market rent to the dollar; in-place rent is ahead of UW. NOI is ~4% behind Y1 pace on two identifiable gaps - concessions running ~2x UW ($640/u drag, burning off as the winter cohort rolls) and the unimplemented bulk-internet program (~$450/u, actionable). Opex runs ~$500/u favorable. For Seasons: supports the occupancy-recovery and rent-level assumptions; the caution is concessions - still 5-6% on new leases at 2018-vintage product in mid-2026, vs Seasons UW burning to 3.0% in Y1.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Development Feasibility — Cost Build-Up, Pro Forma, and Pencil Rents</t>
   </si>
   <si>
@@ -509,9 +666,6 @@
   </si>
   <si>
     <t xml:space="preserve">(1,959,830 − 331,600 embedded taxes)/256.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RE taxes</t>
   </si>
   <si>
     <t xml:space="preserve">Marketed: embedded est. Normalized: 0.45% x 95% of closed-form value.</t>
@@ -1467,6 +1621,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1497,10 +1655,6 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -1908,6 +2062,327 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:F39"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="14" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="C6" s="8" t="n">
+        <v>1130</v>
+      </c>
+      <c r="D6" s="8" t="n">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="C7" s="8" t="n">
+        <v>228</v>
+      </c>
+      <c r="D7" s="8" t="n">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="C8" s="8" t="n">
+        <v>507</v>
+      </c>
+      <c r="D8" s="8" t="n">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="6" t="s">
+        <v>404</v>
+      </c>
+      <c r="C9" s="8" t="n">
+        <v>309</v>
+      </c>
+      <c r="D9" s="8" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="14" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="13" t="s">
+        <v>408</v>
+      </c>
+      <c r="C13" s="8" t="n">
+        <v>552</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="13" t="s">
+        <v>410</v>
+      </c>
+      <c r="C14" s="8" t="n">
+        <v>213</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
+        <v>411</v>
+      </c>
+      <c r="C15" s="8" t="n">
+        <v>212</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
+        <v>413</v>
+      </c>
+      <c r="C16" s="8" t="n">
+        <v>164</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="s">
+        <v>415</v>
+      </c>
+      <c r="C17" s="8" t="n">
+        <v>72</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="18" t="s">
+        <v>416</v>
+      </c>
+      <c r="C18" s="33" t="n">
+        <f aca="false">SUM(C13:C17)</f>
+        <v>1213</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="14" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>406</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="13" t="s">
+        <v>418</v>
+      </c>
+      <c r="C22" s="8" t="n">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="13" t="s">
+        <v>419</v>
+      </c>
+      <c r="C23" s="8" t="n">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="13" t="s">
+        <v>420</v>
+      </c>
+      <c r="C24" s="8" t="n">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="13" t="s">
+        <v>421</v>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="13" t="s">
+        <v>422</v>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="13" t="s">
+        <v>423</v>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>424</v>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="13" t="s">
+        <v>426</v>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="13" t="s">
+        <v>427</v>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="13" t="s">
+        <v>428</v>
+      </c>
+      <c r="C32" s="8" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="13" t="s">
+        <v>429</v>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="13" t="s">
+        <v>430</v>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="6" t="s">
+        <v>431</v>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="18" t="s">
+        <v>432</v>
+      </c>
+      <c r="C36" s="33" t="n">
+        <f aca="false">SUM(C22:C35)</f>
+        <v>3428</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="16" t="s">
+        <v>433</v>
+      </c>
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="16"/>
+      <c r="C39" s="16"/>
+      <c r="D39" s="16"/>
+      <c r="E39" s="16"/>
+      <c r="F39" s="16"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B38:F39"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:C14"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -1918,84 +2393,84 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>383</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="34" t="s">
-        <v>384</v>
+        <v>435</v>
       </c>
       <c r="C4" s="35" t="s">
-        <v>385</v>
+        <v>436</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="34" t="s">
-        <v>386</v>
+        <v>437</v>
       </c>
       <c r="C5" s="35" t="s">
-        <v>387</v>
+        <v>438</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="34" t="s">
-        <v>388</v>
+        <v>439</v>
       </c>
       <c r="C6" s="35" t="s">
-        <v>389</v>
+        <v>440</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="34" t="s">
-        <v>390</v>
+        <v>441</v>
       </c>
       <c r="C7" s="35" t="s">
-        <v>391</v>
+        <v>442</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="34" t="s">
-        <v>392</v>
+        <v>443</v>
       </c>
       <c r="C8" s="35" t="s">
-        <v>393</v>
+        <v>444</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="34" t="s">
-        <v>394</v>
+        <v>445</v>
       </c>
       <c r="C9" s="35" t="s">
-        <v>395</v>
+        <v>446</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="34" t="s">
-        <v>396</v>
+        <v>447</v>
       </c>
       <c r="C10" s="35" t="s">
-        <v>397</v>
+        <v>448</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="34" t="s">
-        <v>398</v>
+        <v>449</v>
       </c>
       <c r="C11" s="35" t="s">
-        <v>399</v>
+        <v>450</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="34" t="s">
-        <v>400</v>
+        <v>451</v>
       </c>
       <c r="C12" s="35" t="s">
-        <v>401</v>
+        <v>452</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="29" t="s">
-        <v>402</v>
+        <v>453</v>
       </c>
     </row>
   </sheetData>
@@ -3067,13 +3542,13 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:I54"/>
+  <dimension ref="B2:G43"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="50"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3081,923 +3556,603 @@
         <v>118</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
         <v>120</v>
       </c>
+      <c r="C5" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="G5" s="5" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="F6" s="5" t="s">
+      <c r="B6" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="G6" s="5" t="s">
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="13" t="s">
         <v>126</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="C7" s="9" t="n">
+        <v>20756</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>20682</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>20682</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <f aca="false">E7/C7-1</f>
+        <v>-0.00356523414916166</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>127</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>128</v>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>9092960</v>
-      </c>
-      <c r="D7" s="10" t="n">
-        <f aca="false">C7/256</f>
-        <v>35519.375</v>
-      </c>
-      <c r="E7" s="12" t="n">
-        <f aca="false">C7/240380</f>
-        <v>37.8274398868458</v>
-      </c>
-      <c r="F7" s="9" t="n">
-        <v>2448783</v>
-      </c>
-      <c r="G7" s="10" t="n">
-        <f aca="false">F7/162</f>
-        <v>15115.9444444444</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <f aca="false">F7/147057</f>
-        <v>16.651930883943</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>-205</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>-581</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>-519</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <f aca="false">E8/C8-1</f>
+        <v>1.53170731707317</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="C8" s="9" t="n">
-        <v>54579077</v>
-      </c>
-      <c r="D8" s="10" t="n">
-        <f aca="false">C8/256</f>
-        <v>213199.51953125</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <f aca="false">C8/240380</f>
-        <v>227.053319743739</v>
-      </c>
-      <c r="F8" s="9" t="n">
-        <v>31439373</v>
-      </c>
-      <c r="G8" s="10" t="n">
-        <f aca="false">F8/162</f>
-        <v>194070.203703704</v>
-      </c>
-      <c r="H8" s="12" t="n">
-        <f aca="false">F8/147057</f>
-        <v>213.790387400804</v>
-      </c>
-      <c r="I8" s="2" t="s">
+      <c r="C9" s="9" t="n">
+        <v>-514</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>-856</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>-1154</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <f aca="false">E9/C9-1</f>
+        <v>1.24513618677043</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>131</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="13" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>1500605</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <f aca="false">C9/256</f>
-        <v>5861.73828125</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <f aca="false">C9/240380</f>
-        <v>6.24263665862385</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>133</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C10" s="9" t="n">
-        <v>4459159</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <f aca="false">C10/256</f>
-        <v>17418.58984375</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <f aca="false">C10/240380</f>
-        <v>18.5504576087861</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>135</v>
+        <v>-1465</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>-1854</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>-1261</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <f aca="false">E10/C10-1</f>
+        <v>-0.139249146757679</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C11" s="9" t="n">
-        <v>3686917</v>
-      </c>
-      <c r="D11" s="10" t="n">
-        <f aca="false">C11/256</f>
-        <v>14402.01953125</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <f aca="false">C11/240380</f>
-        <v>15.3378692070888</v>
-      </c>
-      <c r="F11" s="9" t="n">
-        <v>3714573</v>
-      </c>
-      <c r="G11" s="10" t="n">
-        <f aca="false">F11/162</f>
-        <v>22929.462962963</v>
-      </c>
-      <c r="H11" s="12" t="n">
-        <f aca="false">F11/147057</f>
-        <v>25.2594096166792</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>137</v>
-      </c>
+        <v>18059</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>17398</v>
+      </c>
+      <c r="E11" s="9" t="n">
+        <v>17759</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <f aca="false">E11/C11-1</f>
+        <v>-0.0166122155158093</v>
+      </c>
+      <c r="G11" s="2"/>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2803</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>2347</v>
+      </c>
+      <c r="E12" s="9" t="n">
+        <v>2258</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <f aca="false">E12/C12-1</f>
+        <v>-0.194434534427399</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>20862</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>19745</v>
+      </c>
+      <c r="E13" s="9" t="n">
+        <v>20017</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <f aca="false">E13/C13-1</f>
+        <v>-0.0405042661298054</v>
+      </c>
+      <c r="G13" s="2"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="14" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="13" t="s">
         <v>138</v>
       </c>
-      <c r="C12" s="9" t="n">
-        <v>2658062</v>
-      </c>
-      <c r="D12" s="10" t="n">
-        <f aca="false">C12/256</f>
-        <v>10383.0546875</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <f aca="false">C12/240380</f>
-        <v>11.0577502288044</v>
-      </c>
-      <c r="F12" s="9" t="n">
-        <v>638854</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <f aca="false">F12/162</f>
-        <v>3943.54320987654</v>
-      </c>
-      <c r="H12" s="12" t="n">
-        <f aca="false">F12/147057</f>
-        <v>4.34426106883725</v>
-      </c>
-      <c r="I12" s="2" t="s">
+      <c r="C15" s="9" t="n">
+        <v>1797</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>1461</v>
+      </c>
+      <c r="E15" s="9" t="n">
+        <v>1436</v>
+      </c>
+      <c r="F15" s="15" t="n">
+        <f aca="false">E15/C15-1</f>
+        <v>-0.200890372843628</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>347</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>365</v>
+      </c>
+      <c r="E16" s="9" t="n">
+        <v>481</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <f aca="false">E16/C16-1</f>
+        <v>0.386167146974063</v>
+      </c>
+      <c r="G16" s="2"/>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="C13" s="9" t="n">
-        <v>1982845</v>
-      </c>
-      <c r="D13" s="10" t="n">
-        <f aca="false">C13/256</f>
-        <v>7745.48828125</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <f aca="false">C13/240380</f>
-        <v>8.24879357683668</v>
-      </c>
-      <c r="F13" s="9" t="n">
-        <v>3450136</v>
-      </c>
-      <c r="G13" s="10" t="n">
-        <f aca="false">F13/162</f>
-        <v>21297.1358024691</v>
-      </c>
-      <c r="H13" s="12" t="n">
-        <f aca="false">F13/147057</f>
-        <v>23.4612157190749</v>
-      </c>
-      <c r="I13" s="2" t="s">
+      <c r="C17" s="9" t="n">
+        <v>399</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>421</v>
+      </c>
+      <c r="E17" s="9" t="n">
+        <v>405</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <f aca="false">E17/C17-1</f>
+        <v>0.0150375939849625</v>
+      </c>
+      <c r="G17" s="2"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="13" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="17" t="s">
+      <c r="C18" s="9" t="n">
+        <v>228</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>141</v>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>180</v>
+      </c>
+      <c r="F18" s="15" t="n">
+        <f aca="false">E18/C18-1</f>
+        <v>-0.210526315789474</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>157</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>120</v>
+      </c>
+      <c r="E19" s="9" t="n">
+        <v>169</v>
+      </c>
+      <c r="F19" s="15" t="n">
+        <f aca="false">E19/C19-1</f>
+        <v>0.0764331210191083</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
         <v>142</v>
       </c>
-      <c r="C14" s="18" t="n">
-        <f aca="false">SUM(C7:C13)</f>
-        <v>77959625</v>
-      </c>
-      <c r="D14" s="18" t="n">
-        <f aca="false">C14/256</f>
-        <v>304529.78515625</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <f aca="false">C14/240380</f>
-        <v>324.318266910725</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <f aca="false">SUM(F7:F13)</f>
-        <v>41691719</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <f aca="false">F14/162</f>
-        <v>257356.290123457</v>
-      </c>
-      <c r="H14" s="19" t="n">
-        <f aca="false">F14/147057</f>
-        <v>283.507204689338</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="17" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="10" t="n">
-        <f aca="false">C14-C13</f>
-        <v>75976780</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="14" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="5" t="s">
-        <v>148</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>149</v>
-      </c>
       <c r="C20" s="9" t="n">
-        <v>2069</v>
+        <v>716</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>2069</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>150</v>
-      </c>
+        <v>710</v>
+      </c>
+      <c r="E20" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="F20" s="15" t="n">
+        <f aca="false">E20/C20-1</f>
+        <v>0.159217877094972</v>
+      </c>
+      <c r="G20" s="2"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>151</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <f aca="false">C20*12</f>
-        <v>24828</v>
-      </c>
-      <c r="D21" s="10" t="n">
-        <f aca="false">D20*12</f>
-        <v>24828</v>
-      </c>
-      <c r="E21" s="2"/>
-    </row>
-    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>106</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>559</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>584</v>
+      </c>
+      <c r="E21" s="9" t="n">
+        <v>600</v>
+      </c>
+      <c r="F21" s="15" t="n">
+        <f aca="false">E21/C21-1</f>
+        <v>0.073345259391771</v>
+      </c>
+      <c r="G21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>152</v>
+        <v>107</v>
       </c>
       <c r="C22" s="9" t="n">
-        <v>4207</v>
-      </c>
-      <c r="D22" s="20" t="n">
-        <f aca="false">4_Emblem_Norm!C29</f>
-        <v>3398</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>153</v>
+        <v>522</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>475</v>
+      </c>
+      <c r="E22" s="9" t="n">
+        <v>470</v>
+      </c>
+      <c r="F22" s="15" t="n">
+        <f aca="false">E22/C22-1</f>
+        <v>-0.0996168582375479</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>620</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>551</v>
+      </c>
+      <c r="E23" s="9" t="n">
+        <v>481</v>
+      </c>
+      <c r="F23" s="15" t="n">
+        <f aca="false">E23/C23-1</f>
+        <v>-0.224193548387097</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C24" s="9" t="n">
+        <v>1191</v>
+      </c>
+      <c r="D24" s="9" t="n">
+        <v>1191</v>
+      </c>
+      <c r="E24" s="9" t="n">
+        <v>1191</v>
+      </c>
+      <c r="F24" s="15" t="n">
+        <f aca="false">E24/C24-1</f>
+        <v>0</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C25" s="9" t="n">
+        <v>6536</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>6019</v>
+      </c>
+      <c r="E25" s="9" t="n">
+        <v>6246</v>
+      </c>
+      <c r="F25" s="15" t="n">
+        <f aca="false">E25/C25-1</f>
+        <v>-0.0443696450428397</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C26" s="9" t="n">
+        <v>14335</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>13726</v>
+      </c>
+      <c r="E26" s="9" t="n">
+        <v>13772</v>
+      </c>
+      <c r="F26" s="15" t="n">
+        <f aca="false">E26/C26-1</f>
+        <v>-0.0392745029647715</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="14" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="9" t="n">
+        <v>271</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="9" t="n">
+        <v>1668</v>
+      </c>
+      <c r="D29" s="9" t="n">
+        <v>1680</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="13" t="s">
         <v>154</v>
       </c>
-      <c r="C23" s="10" t="n">
-        <f aca="false">C21+C22</f>
-        <v>29035</v>
-      </c>
-      <c r="D23" s="10" t="n">
-        <f aca="false">D21+D22</f>
-        <v>28226</v>
-      </c>
-      <c r="E23" s="2"/>
-    </row>
-    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
+      <c r="C30" s="9" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D30" s="9" t="n">
+        <v>1724</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C24" s="10" t="n">
-        <f aca="false">-C23*0.0587</f>
-        <v>-1704.3545</v>
-      </c>
-      <c r="D24" s="10" t="n">
-        <f aca="false">-D23*0.0587</f>
-        <v>-1656.8662</v>
-      </c>
-      <c r="E24" s="2" t="s">
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="13" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
+      <c r="C31" s="9" t="n">
+        <v>1730</v>
+      </c>
+      <c r="D31" s="9" t="n">
+        <v>1731</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C25" s="10" t="n">
-        <f aca="false">C23+C24</f>
-        <v>27330.6455</v>
-      </c>
-      <c r="D25" s="10" t="n">
-        <f aca="false">D23+D24</f>
-        <v>26569.1338</v>
-      </c>
-      <c r="E25" s="2"/>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="13" t="s">
         <v>158</v>
       </c>
-      <c r="C26" s="10" t="n">
-        <f aca="false">-6360</f>
-        <v>-6360</v>
-      </c>
-      <c r="D26" s="10" t="n">
-        <f aca="false">-6360</f>
-        <v>-6360</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="D32" s="9" t="n">
+        <v>1575</v>
+      </c>
+      <c r="G32" s="2" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="27" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>160</v>
-      </c>
-      <c r="C27" s="9" t="n">
-        <v>-1295</v>
-      </c>
-      <c r="D27" s="20" t="n">
-        <f aca="false">-4_Emblem_Norm!C46</f>
-        <v>-1521.56798326505</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="C28" s="10" t="n">
-        <f aca="false">SUM(C25:C27)</f>
-        <v>19675.6455</v>
-      </c>
-      <c r="D28" s="10" t="n">
-        <f aca="false">SUM(D25:D27)</f>
-        <v>18687.565816735</v>
-      </c>
-      <c r="E28" s="2"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="C29" s="10" t="n">
-        <f aca="false">C28*256</f>
-        <v>5036965.248</v>
-      </c>
-      <c r="D29" s="10" t="n">
-        <f aca="false">D28*256</f>
-        <v>4784016.84908415</v>
-      </c>
-      <c r="E29" s="2"/>
-    </row>
-    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="C30" s="21" t="n">
-        <f aca="false">C29/$C$16</f>
-        <v>0.066296113733696</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <f aca="false">D29/$C$16</f>
-        <v>0.0629668281425476</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="C31" s="21" t="n">
-        <f aca="false">C29/$C$14</f>
-        <v>0.0646099214561384</v>
-      </c>
-      <c r="D31" s="21" t="n">
-        <f aca="false">D29/$C$14</f>
-        <v>0.0613653137644537</v>
-      </c>
-      <c r="E31" s="2"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="14" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="13" t="s">
+        <v>161</v>
+      </c>
+      <c r="D34" s="9" t="n">
+        <v>1366</v>
+      </c>
+      <c r="E34" s="9" t="n">
+        <v>1509</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D35" s="9" t="n">
+        <v>1713</v>
+      </c>
+      <c r="E35" s="9" t="n">
+        <v>1802</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="13" t="s">
+        <v>165</v>
+      </c>
+      <c r="D36" s="9" t="n">
+        <v>1762</v>
+      </c>
+      <c r="E36" s="9" t="n">
+        <v>1838</v>
+      </c>
+      <c r="G36" s="2" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="16" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="13" t="s">
         <v>167</v>
       </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
-      <c r="E34" s="16"/>
-      <c r="F34" s="16"/>
-      <c r="G34" s="16"/>
-      <c r="H34" s="16"/>
-      <c r="I34" s="16"/>
-    </row>
-    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
+      <c r="D37" s="9" t="n">
+        <v>1940</v>
+      </c>
+      <c r="E37" s="9" t="n">
+        <v>2180</v>
+      </c>
+      <c r="G37" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C35" s="5" t="s">
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B39" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="D35" s="5" t="s">
-        <v>170</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>171</v>
-      </c>
-      <c r="F35" s="5" t="s">
-        <v>172</v>
-      </c>
-      <c r="G35" s="5" t="s">
-        <v>173</v>
-      </c>
-      <c r="H35" s="5" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="C36" s="10" t="n">
-        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>1857.9703062323</v>
-      </c>
-      <c r="D36" s="10" t="n">
-        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>1925.38697289896</v>
-      </c>
-      <c r="E36" s="10" t="n">
-        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>1980.55363956563</v>
-      </c>
-      <c r="F36" s="12" t="n">
-        <f aca="false">D36/938.98</f>
-        <v>2.05050903416363</v>
-      </c>
-      <c r="G36" s="15" t="n">
-        <f aca="false">D36/1885-1</f>
-        <v>0.0214254498137745</v>
-      </c>
-      <c r="H36" s="15" t="n">
-        <f aca="false">F36/2.021-1</f>
-        <v>0.0146012044352448</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C37" s="10" t="n">
-        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>1923.65612568301</v>
-      </c>
-      <c r="D37" s="10" t="n">
-        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>1991.07279234968</v>
-      </c>
-      <c r="E37" s="10" t="n">
-        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2046.23945901635</v>
-      </c>
-      <c r="F37" s="12" t="n">
-        <f aca="false">D37/938.98</f>
-        <v>2.12046347350282</v>
-      </c>
-      <c r="G37" s="15" t="n">
-        <f aca="false">D37/1885-1</f>
-        <v>0.0562720383817932</v>
-      </c>
-      <c r="H37" s="15" t="n">
-        <f aca="false">F37/2.021-1</f>
-        <v>0.0492149794670076</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="22" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="C38" s="10" t="n">
-        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>1989.34194513373</v>
-      </c>
-      <c r="D38" s="10" t="n">
-        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>2056.7586118004</v>
-      </c>
-      <c r="E38" s="10" t="n">
-        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2111.92527846706</v>
-      </c>
-      <c r="F38" s="12" t="n">
-        <f aca="false">D38/938.98</f>
-        <v>2.19041791284202</v>
-      </c>
-      <c r="G38" s="15" t="n">
-        <f aca="false">D38/1885-1</f>
-        <v>0.0911186269498117</v>
-      </c>
-      <c r="H38" s="15" t="n">
-        <f aca="false">F38/2.021-1</f>
-        <v>0.0838287544987704</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="22" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C39" s="10" t="n">
-        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>2055.02776458444</v>
-      </c>
-      <c r="D39" s="10" t="n">
-        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>2122.44443125111</v>
-      </c>
-      <c r="E39" s="10" t="n">
-        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2177.61109791778</v>
-      </c>
-      <c r="F39" s="12" t="n">
-        <f aca="false">D39/938.98</f>
-        <v>2.26037235218121</v>
-      </c>
-      <c r="G39" s="15" t="n">
-        <f aca="false">D39/1885-1</f>
-        <v>0.125965215517831</v>
-      </c>
-      <c r="H39" s="15" t="n">
-        <f aca="false">F39/2.021-1</f>
-        <v>0.118442529530533</v>
-      </c>
+      <c r="C39" s="17"/>
+      <c r="D39" s="17"/>
+      <c r="E39" s="17"/>
+      <c r="F39" s="17"/>
+      <c r="G39" s="17"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="22" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="C40" s="10" t="n">
-        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>2120.71358403516</v>
-      </c>
-      <c r="D40" s="10" t="n">
-        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>2188.13025070183</v>
-      </c>
-      <c r="E40" s="10" t="n">
-        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2243.29691736849</v>
-      </c>
-      <c r="F40" s="12" t="n">
-        <f aca="false">D40/938.98</f>
-        <v>2.3303267915204</v>
-      </c>
-      <c r="G40" s="15" t="n">
-        <f aca="false">D40/1885-1</f>
-        <v>0.160811804085849</v>
-      </c>
-      <c r="H40" s="15" t="n">
-        <f aca="false">F40/2.021-1</f>
-        <v>0.153056304562296</v>
-      </c>
+      <c r="B40" s="17"/>
+      <c r="C40" s="17"/>
+      <c r="D40" s="17"/>
+      <c r="E40" s="17"/>
+      <c r="F40" s="17"/>
+      <c r="G40" s="17"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="22" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="C41" s="10" t="n">
-        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>2186.39940348587</v>
-      </c>
-      <c r="D41" s="10" t="n">
-        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>2253.81607015254</v>
-      </c>
-      <c r="E41" s="10" t="n">
-        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2308.98273681921</v>
-      </c>
-      <c r="F41" s="12" t="n">
-        <f aca="false">D41/938.98</f>
-        <v>2.40028123085959</v>
-      </c>
-      <c r="G41" s="15" t="n">
-        <f aca="false">D41/1885-1</f>
-        <v>0.195658392653868</v>
-      </c>
-      <c r="H41" s="15" t="n">
-        <f aca="false">F41/2.021-1</f>
-        <v>0.18767007959406</v>
-      </c>
+      <c r="B41" s="17"/>
+      <c r="C41" s="17"/>
+      <c r="D41" s="17"/>
+      <c r="E41" s="17"/>
+      <c r="F41" s="17"/>
+      <c r="G41" s="17"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="22" t="n">
-        <v>0.0725</v>
-      </c>
-      <c r="C42" s="10" t="n">
-        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
-        <v>2252.08522293659</v>
-      </c>
-      <c r="D42" s="10" t="n">
-        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
-        <v>2319.50188960326</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
-        <v>2374.66855626992</v>
-      </c>
-      <c r="F42" s="12" t="n">
-        <f aca="false">D42/938.98</f>
-        <v>2.47023567019879</v>
-      </c>
-      <c r="G42" s="15" t="n">
-        <f aca="false">D42/1885-1</f>
-        <v>0.230504981221887</v>
-      </c>
-      <c r="H42" s="15" t="n">
-        <f aca="false">F42/2.021-1</f>
-        <v>0.222283854625822</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="14" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="17" t="s">
-        <v>176</v>
-      </c>
-      <c r="C45" s="23" t="n">
-        <v>2026</v>
-      </c>
-      <c r="D45" s="23" t="n">
-        <v>2027</v>
-      </c>
-      <c r="E45" s="23" t="n">
-        <v>2028</v>
-      </c>
-      <c r="F45" s="23" t="n">
-        <v>2029</v>
-      </c>
-      <c r="G45" s="23" t="n">
-        <v>2030</v>
-      </c>
-      <c r="H45" s="23" t="n">
-        <v>2031</v>
-      </c>
-      <c r="I45" s="23" t="n">
-        <v>2032</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="24" t="s">
-        <v>177</v>
-      </c>
-      <c r="D46" s="9" t="n">
-        <v>1885</v>
-      </c>
-      <c r="E46" s="9" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F46" s="9" t="n">
-        <v>2038</v>
-      </c>
-      <c r="G46" s="9" t="n">
-        <v>2110</v>
-      </c>
-      <c r="H46" s="9" t="n">
-        <v>2184</v>
-      </c>
-      <c r="I46" s="9" t="n">
-        <v>2249</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="24" t="s">
-        <v>178</v>
-      </c>
-      <c r="C47" s="10" t="n">
-        <f aca="false">$D$37*1.03^0</f>
-        <v>1991.07279234968</v>
-      </c>
-      <c r="D47" s="10" t="n">
-        <f aca="false">$D$37*1.03^1</f>
-        <v>2050.80497612017</v>
-      </c>
-      <c r="E47" s="10" t="n">
-        <f aca="false">$D$37*1.03^2</f>
-        <v>2112.32912540378</v>
-      </c>
-      <c r="F47" s="10" t="n">
-        <f aca="false">$D$37*1.03^3</f>
-        <v>2175.69899916589</v>
-      </c>
-      <c r="G47" s="10" t="n">
-        <f aca="false">$D$37*1.03^4</f>
-        <v>2240.96996914087</v>
-      </c>
-      <c r="H47" s="10" t="n">
-        <f aca="false">$D$37*1.03^5</f>
-        <v>2308.19906821509</v>
-      </c>
-      <c r="I47" s="10" t="n">
-        <f aca="false">$D$37*1.03^6</f>
-        <v>2377.44504026154</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="C48" s="10" t="n">
-        <f aca="false">$D$39*1.03^0</f>
-        <v>2122.44443125111</v>
-      </c>
-      <c r="D48" s="10" t="n">
-        <f aca="false">$D$39*1.03^1</f>
-        <v>2186.11776418864</v>
-      </c>
-      <c r="E48" s="10" t="n">
-        <f aca="false">$D$39*1.03^2</f>
-        <v>2251.7012971143</v>
-      </c>
-      <c r="F48" s="10" t="n">
-        <f aca="false">$D$39*1.03^3</f>
-        <v>2319.25233602773</v>
-      </c>
-      <c r="G48" s="10" t="n">
-        <f aca="false">$D$39*1.03^4</f>
-        <v>2388.82990610857</v>
-      </c>
-      <c r="H48" s="10" t="n">
-        <f aca="false">$D$39*1.03^5</f>
-        <v>2460.49480329182</v>
-      </c>
-      <c r="I48" s="10" t="n">
-        <f aca="false">$D$39*1.03^6</f>
-        <v>2534.30964739058</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="D49" s="15" t="n">
-        <f aca="false">D46/D47-1</f>
-        <v>-0.0808487291823574</v>
-      </c>
-      <c r="E49" s="15" t="n">
-        <f aca="false">E46/E47-1</f>
-        <v>-0.072114294866174</v>
-      </c>
-      <c r="F49" s="15" t="n">
-        <f aca="false">F46/F47-1</f>
-        <v>-0.0632895447480002</v>
-      </c>
-      <c r="G49" s="15" t="n">
-        <f aca="false">G46/G47-1</f>
-        <v>-0.0584434289367457</v>
-      </c>
-      <c r="H49" s="15" t="n">
-        <f aca="false">H46/H47-1</f>
-        <v>-0.0538077802410402</v>
-      </c>
-      <c r="I49" s="15" t="n">
-        <f aca="false">I46/I47-1</f>
-        <v>-0.0540265024370086</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="17" t="s">
-        <v>181</v>
-      </c>
-      <c r="D50" s="15" t="n">
-        <f aca="false">D46/D48-1</f>
-        <v>-0.137740870652685</v>
-      </c>
-      <c r="E50" s="15" t="n">
-        <f aca="false">E46/E48-1</f>
-        <v>-0.129547066250811</v>
-      </c>
-      <c r="F50" s="15" t="n">
-        <f aca="false">F46/F48-1</f>
-        <v>-0.121268536268651</v>
-      </c>
-      <c r="G50" s="15" t="n">
-        <f aca="false">G46/G48-1</f>
-        <v>-0.116722377510244</v>
-      </c>
-      <c r="H50" s="15" t="n">
-        <f aca="false">H46/H48-1</f>
-        <v>-0.112373658713649</v>
-      </c>
-      <c r="I50" s="15" t="n">
-        <f aca="false">I46/I48-1</f>
-        <v>-0.112578842796239</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="C52" s="25"/>
-      <c r="D52" s="25"/>
-      <c r="E52" s="25"/>
-      <c r="F52" s="25"/>
-      <c r="G52" s="25"/>
-      <c r="H52" s="25"/>
-      <c r="I52" s="25"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="25"/>
-      <c r="C53" s="25"/>
-      <c r="D53" s="25"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="25"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="25"/>
-      <c r="I53" s="25"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="25"/>
-      <c r="C54" s="25"/>
-      <c r="D54" s="25"/>
-      <c r="E54" s="25"/>
-      <c r="F54" s="25"/>
-      <c r="G54" s="25"/>
-      <c r="H54" s="25"/>
-      <c r="I54" s="25"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="17"/>
+      <c r="D42" s="17"/>
+      <c r="E42" s="17"/>
+      <c r="F42" s="17"/>
+      <c r="G42" s="17"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="17"/>
+      <c r="C43" s="17"/>
+      <c r="D43" s="17"/>
+      <c r="E43" s="17"/>
+      <c r="F43" s="17"/>
+      <c r="G43" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B34:I34"/>
-    <mergeCell ref="B52:I54"/>
+  <mergeCells count="1">
+    <mergeCell ref="B39:G43"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4014,6 +4169,953 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:I54"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="46"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="14" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G6" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="H6" s="5" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="13" t="s">
+        <v>180</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>9092960</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <f aca="false">C7/256</f>
+        <v>35519.375</v>
+      </c>
+      <c r="E7" s="12" t="n">
+        <f aca="false">C7/240380</f>
+        <v>37.8274398868458</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>2448783</v>
+      </c>
+      <c r="G7" s="10" t="n">
+        <f aca="false">F7/162</f>
+        <v>15115.9444444444</v>
+      </c>
+      <c r="H7" s="12" t="n">
+        <f aca="false">F7/147057</f>
+        <v>16.651930883943</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>54579077</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <f aca="false">C8/256</f>
+        <v>213199.51953125</v>
+      </c>
+      <c r="E8" s="12" t="n">
+        <f aca="false">C8/240380</f>
+        <v>227.053319743739</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>31439373</v>
+      </c>
+      <c r="G8" s="10" t="n">
+        <f aca="false">F8/162</f>
+        <v>194070.203703704</v>
+      </c>
+      <c r="H8" s="12" t="n">
+        <f aca="false">F8/147057</f>
+        <v>213.790387400804</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>1500605</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <f aca="false">C9/256</f>
+        <v>5861.73828125</v>
+      </c>
+      <c r="E9" s="12" t="n">
+        <f aca="false">C9/240380</f>
+        <v>6.24263665862385</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="13" t="s">
+        <v>186</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>4459159</v>
+      </c>
+      <c r="D10" s="10" t="n">
+        <f aca="false">C10/256</f>
+        <v>17418.58984375</v>
+      </c>
+      <c r="E10" s="12" t="n">
+        <f aca="false">C10/240380</f>
+        <v>18.5504576087861</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>3686917</v>
+      </c>
+      <c r="D11" s="10" t="n">
+        <f aca="false">C11/256</f>
+        <v>14402.01953125</v>
+      </c>
+      <c r="E11" s="12" t="n">
+        <f aca="false">C11/240380</f>
+        <v>15.3378692070888</v>
+      </c>
+      <c r="F11" s="9" t="n">
+        <v>3714573</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <f aca="false">F11/162</f>
+        <v>22929.462962963</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <f aca="false">F11/147057</f>
+        <v>25.2594096166792</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="13" t="s">
+        <v>190</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>2658062</v>
+      </c>
+      <c r="D12" s="10" t="n">
+        <f aca="false">C12/256</f>
+        <v>10383.0546875</v>
+      </c>
+      <c r="E12" s="12" t="n">
+        <f aca="false">C12/240380</f>
+        <v>11.0577502288044</v>
+      </c>
+      <c r="F12" s="9" t="n">
+        <v>638854</v>
+      </c>
+      <c r="G12" s="10" t="n">
+        <f aca="false">F12/162</f>
+        <v>3943.54320987654</v>
+      </c>
+      <c r="H12" s="12" t="n">
+        <f aca="false">F12/147057</f>
+        <v>4.34426106883725</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>1982845</v>
+      </c>
+      <c r="D13" s="10" t="n">
+        <f aca="false">C13/256</f>
+        <v>7745.48828125</v>
+      </c>
+      <c r="E13" s="12" t="n">
+        <f aca="false">C13/240380</f>
+        <v>8.24879357683668</v>
+      </c>
+      <c r="F13" s="9" t="n">
+        <v>3450136</v>
+      </c>
+      <c r="G13" s="10" t="n">
+        <f aca="false">F13/162</f>
+        <v>21297.1358024691</v>
+      </c>
+      <c r="H13" s="12" t="n">
+        <f aca="false">F13/147057</f>
+        <v>23.4612157190749</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="18" t="s">
+        <v>194</v>
+      </c>
+      <c r="C14" s="19" t="n">
+        <f aca="false">SUM(C7:C13)</f>
+        <v>77959625</v>
+      </c>
+      <c r="D14" s="19" t="n">
+        <f aca="false">C14/256</f>
+        <v>304529.78515625</v>
+      </c>
+      <c r="E14" s="20" t="n">
+        <f aca="false">C14/240380</f>
+        <v>324.318266910725</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <f aca="false">SUM(F7:F13)</f>
+        <v>41691719</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <f aca="false">F14/162</f>
+        <v>257356.290123457</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <f aca="false">F14/147057</f>
+        <v>283.507204689338</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="18" t="s">
+        <v>196</v>
+      </c>
+      <c r="C16" s="10" t="n">
+        <f aca="false">C14-C13</f>
+        <v>75976780</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="14" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C19" s="5" t="s">
+        <v>199</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="E19" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="64.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="13" t="s">
+        <v>201</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>2069</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2069</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <f aca="false">C20*12</f>
+        <v>24828</v>
+      </c>
+      <c r="D21" s="10" t="n">
+        <f aca="false">D20*12</f>
+        <v>24828</v>
+      </c>
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>4207</v>
+      </c>
+      <c r="D22" s="21" t="n">
+        <f aca="false">4_Emblem_Norm!C29</f>
+        <v>3398</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="13" t="s">
+        <v>206</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <f aca="false">C21+C22</f>
+        <v>29035</v>
+      </c>
+      <c r="D23" s="10" t="n">
+        <f aca="false">D21+D22</f>
+        <v>28226</v>
+      </c>
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <f aca="false">-C23*0.0587</f>
+        <v>-1704.3545</v>
+      </c>
+      <c r="D24" s="10" t="n">
+        <f aca="false">-D23*0.0587</f>
+        <v>-1656.8662</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="13" t="s">
+        <v>209</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <f aca="false">C23+C24</f>
+        <v>27330.6455</v>
+      </c>
+      <c r="D25" s="10" t="n">
+        <f aca="false">D23+D24</f>
+        <v>26569.1338</v>
+      </c>
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="13" t="s">
+        <v>210</v>
+      </c>
+      <c r="C26" s="10" t="n">
+        <f aca="false">-6360</f>
+        <v>-6360</v>
+      </c>
+      <c r="D26" s="10" t="n">
+        <f aca="false">-6360</f>
+        <v>-6360</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="13" t="s">
+        <v>144</v>
+      </c>
+      <c r="C27" s="9" t="n">
+        <v>-1295</v>
+      </c>
+      <c r="D27" s="21" t="n">
+        <f aca="false">-4_Emblem_Norm!C46</f>
+        <v>-1521.56798326505</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="C28" s="10" t="n">
+        <f aca="false">SUM(C25:C27)</f>
+        <v>19675.6455</v>
+      </c>
+      <c r="D28" s="10" t="n">
+        <f aca="false">SUM(D25:D27)</f>
+        <v>18687.565816735</v>
+      </c>
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C29" s="10" t="n">
+        <f aca="false">C28*256</f>
+        <v>5036965.248</v>
+      </c>
+      <c r="D29" s="10" t="n">
+        <f aca="false">D28*256</f>
+        <v>4784016.84908415</v>
+      </c>
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <f aca="false">C29/$C$16</f>
+        <v>0.066296113733696</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <f aca="false">D29/$C$16</f>
+        <v>0.0629668281425476</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="C31" s="22" t="n">
+        <f aca="false">C29/$C$14</f>
+        <v>0.0646099214561384</v>
+      </c>
+      <c r="D31" s="22" t="n">
+        <f aca="false">D29/$C$14</f>
+        <v>0.0613653137644537</v>
+      </c>
+      <c r="E31" s="2"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="14" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B34" s="16" t="s">
+        <v>218</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+      <c r="E34" s="16"/>
+      <c r="F34" s="16"/>
+      <c r="G34" s="16"/>
+      <c r="H34" s="16"/>
+      <c r="I34" s="16"/>
+    </row>
+    <row r="35" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>219</v>
+      </c>
+      <c r="C35" s="5" t="s">
+        <v>220</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>221</v>
+      </c>
+      <c r="E35" s="5" t="s">
+        <v>222</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>223</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>224</v>
+      </c>
+      <c r="H35" s="5" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="23" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="C36" s="10" t="n">
+        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>1857.9703062323</v>
+      </c>
+      <c r="D36" s="10" t="n">
+        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>1925.38697289896</v>
+      </c>
+      <c r="E36" s="10" t="n">
+        <f aca="false">((B36*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>1980.55363956563</v>
+      </c>
+      <c r="F36" s="12" t="n">
+        <f aca="false">D36/938.98</f>
+        <v>2.05050903416363</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <f aca="false">D36/1885-1</f>
+        <v>0.0214254498137745</v>
+      </c>
+      <c r="H36" s="15" t="n">
+        <f aca="false">F36/2.021-1</f>
+        <v>0.0146012044352448</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="23" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C37" s="10" t="n">
+        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>1923.65612568301</v>
+      </c>
+      <c r="D37" s="10" t="n">
+        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>1991.07279234968</v>
+      </c>
+      <c r="E37" s="10" t="n">
+        <f aca="false">((B37*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2046.23945901635</v>
+      </c>
+      <c r="F37" s="12" t="n">
+        <f aca="false">D37/938.98</f>
+        <v>2.12046347350282</v>
+      </c>
+      <c r="G37" s="15" t="n">
+        <f aca="false">D37/1885-1</f>
+        <v>0.0562720383817932</v>
+      </c>
+      <c r="H37" s="15" t="n">
+        <f aca="false">F37/2.021-1</f>
+        <v>0.0492149794670076</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B38" s="23" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="C38" s="10" t="n">
+        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>1989.34194513373</v>
+      </c>
+      <c r="D38" s="10" t="n">
+        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>2056.7586118004</v>
+      </c>
+      <c r="E38" s="10" t="n">
+        <f aca="false">((B38*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2111.92527846706</v>
+      </c>
+      <c r="F38" s="12" t="n">
+        <f aca="false">D38/938.98</f>
+        <v>2.19041791284202</v>
+      </c>
+      <c r="G38" s="15" t="n">
+        <f aca="false">D38/1885-1</f>
+        <v>0.0911186269498117</v>
+      </c>
+      <c r="H38" s="15" t="n">
+        <f aca="false">F38/2.021-1</f>
+        <v>0.0838287544987704</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="23" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C39" s="10" t="n">
+        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>2055.02776458444</v>
+      </c>
+      <c r="D39" s="10" t="n">
+        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>2122.44443125111</v>
+      </c>
+      <c r="E39" s="10" t="n">
+        <f aca="false">((B39*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2177.61109791778</v>
+      </c>
+      <c r="F39" s="12" t="n">
+        <f aca="false">D39/938.98</f>
+        <v>2.26037235218121</v>
+      </c>
+      <c r="G39" s="15" t="n">
+        <f aca="false">D39/1885-1</f>
+        <v>0.125965215517831</v>
+      </c>
+      <c r="H39" s="15" t="n">
+        <f aca="false">F39/2.021-1</f>
+        <v>0.118442529530533</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="23" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="C40" s="10" t="n">
+        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>2120.71358403516</v>
+      </c>
+      <c r="D40" s="10" t="n">
+        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>2188.13025070183</v>
+      </c>
+      <c r="E40" s="10" t="n">
+        <f aca="false">((B40*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2243.29691736849</v>
+      </c>
+      <c r="F40" s="12" t="n">
+        <f aca="false">D40/938.98</f>
+        <v>2.3303267915204</v>
+      </c>
+      <c r="G40" s="15" t="n">
+        <f aca="false">D40/1885-1</f>
+        <v>0.160811804085849</v>
+      </c>
+      <c r="H40" s="15" t="n">
+        <f aca="false">F40/2.021-1</f>
+        <v>0.153056304562296</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="23" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C41" s="10" t="n">
+        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>2186.39940348587</v>
+      </c>
+      <c r="D41" s="10" t="n">
+        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>2253.81607015254</v>
+      </c>
+      <c r="E41" s="10" t="n">
+        <f aca="false">((B41*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2308.98273681921</v>
+      </c>
+      <c r="F41" s="12" t="n">
+        <f aca="false">D41/938.98</f>
+        <v>2.40028123085959</v>
+      </c>
+      <c r="G41" s="15" t="n">
+        <f aca="false">D41/1885-1</f>
+        <v>0.195658392653868</v>
+      </c>
+      <c r="H41" s="15" t="n">
+        <f aca="false">F41/2.021-1</f>
+        <v>0.18767007959406</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B42" s="23" t="n">
+        <v>0.0725</v>
+      </c>
+      <c r="C42" s="10" t="n">
+        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4207*256)/256/12</f>
+        <v>2252.08522293659</v>
+      </c>
+      <c r="D42" s="10" t="n">
+        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-4_Emblem_Norm!C29*256)/256/12</f>
+        <v>2319.50188960326</v>
+      </c>
+      <c r="E42" s="10" t="n">
+        <f aca="false">((B42*$C$16+((1959830-331600)+4_Emblem_Norm!C45))/0.9413-2736*256)/256/12</f>
+        <v>2374.66855626992</v>
+      </c>
+      <c r="F42" s="12" t="n">
+        <f aca="false">D42/938.98</f>
+        <v>2.47023567019879</v>
+      </c>
+      <c r="G42" s="15" t="n">
+        <f aca="false">D42/1885-1</f>
+        <v>0.230504981221887</v>
+      </c>
+      <c r="H42" s="15" t="n">
+        <f aca="false">F42/2.021-1</f>
+        <v>0.222283854625822</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B44" s="14" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="18" t="s">
+        <v>227</v>
+      </c>
+      <c r="C45" s="24" t="n">
+        <v>2026</v>
+      </c>
+      <c r="D45" s="24" t="n">
+        <v>2027</v>
+      </c>
+      <c r="E45" s="24" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F45" s="24" t="n">
+        <v>2029</v>
+      </c>
+      <c r="G45" s="24" t="n">
+        <v>2030</v>
+      </c>
+      <c r="H45" s="24" t="n">
+        <v>2031</v>
+      </c>
+      <c r="I45" s="24" t="n">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="25" t="s">
+        <v>228</v>
+      </c>
+      <c r="D46" s="9" t="n">
+        <v>1885</v>
+      </c>
+      <c r="E46" s="9" t="n">
+        <v>1960</v>
+      </c>
+      <c r="F46" s="9" t="n">
+        <v>2038</v>
+      </c>
+      <c r="G46" s="9" t="n">
+        <v>2110</v>
+      </c>
+      <c r="H46" s="9" t="n">
+        <v>2184</v>
+      </c>
+      <c r="I46" s="9" t="n">
+        <v>2249</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="25" t="s">
+        <v>229</v>
+      </c>
+      <c r="C47" s="10" t="n">
+        <f aca="false">$D$37*1.03^0</f>
+        <v>1991.07279234968</v>
+      </c>
+      <c r="D47" s="10" t="n">
+        <f aca="false">$D$37*1.03^1</f>
+        <v>2050.80497612017</v>
+      </c>
+      <c r="E47" s="10" t="n">
+        <f aca="false">$D$37*1.03^2</f>
+        <v>2112.32912540378</v>
+      </c>
+      <c r="F47" s="10" t="n">
+        <f aca="false">$D$37*1.03^3</f>
+        <v>2175.69899916589</v>
+      </c>
+      <c r="G47" s="10" t="n">
+        <f aca="false">$D$37*1.03^4</f>
+        <v>2240.96996914087</v>
+      </c>
+      <c r="H47" s="10" t="n">
+        <f aca="false">$D$37*1.03^5</f>
+        <v>2308.19906821509</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <f aca="false">$D$37*1.03^6</f>
+        <v>2377.44504026154</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="C48" s="10" t="n">
+        <f aca="false">$D$39*1.03^0</f>
+        <v>2122.44443125111</v>
+      </c>
+      <c r="D48" s="10" t="n">
+        <f aca="false">$D$39*1.03^1</f>
+        <v>2186.11776418864</v>
+      </c>
+      <c r="E48" s="10" t="n">
+        <f aca="false">$D$39*1.03^2</f>
+        <v>2251.7012971143</v>
+      </c>
+      <c r="F48" s="10" t="n">
+        <f aca="false">$D$39*1.03^3</f>
+        <v>2319.25233602773</v>
+      </c>
+      <c r="G48" s="10" t="n">
+        <f aca="false">$D$39*1.03^4</f>
+        <v>2388.82990610857</v>
+      </c>
+      <c r="H48" s="10" t="n">
+        <f aca="false">$D$39*1.03^5</f>
+        <v>2460.49480329182</v>
+      </c>
+      <c r="I48" s="10" t="n">
+        <f aca="false">$D$39*1.03^6</f>
+        <v>2534.30964739058</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="18" t="s">
+        <v>231</v>
+      </c>
+      <c r="D49" s="15" t="n">
+        <f aca="false">D46/D47-1</f>
+        <v>-0.0808487291823574</v>
+      </c>
+      <c r="E49" s="15" t="n">
+        <f aca="false">E46/E47-1</f>
+        <v>-0.072114294866174</v>
+      </c>
+      <c r="F49" s="15" t="n">
+        <f aca="false">F46/F47-1</f>
+        <v>-0.0632895447480002</v>
+      </c>
+      <c r="G49" s="15" t="n">
+        <f aca="false">G46/G47-1</f>
+        <v>-0.0584434289367457</v>
+      </c>
+      <c r="H49" s="15" t="n">
+        <f aca="false">H46/H47-1</f>
+        <v>-0.0538077802410402</v>
+      </c>
+      <c r="I49" s="15" t="n">
+        <f aca="false">I46/I47-1</f>
+        <v>-0.0540265024370086</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="18" t="s">
+        <v>232</v>
+      </c>
+      <c r="D50" s="15" t="n">
+        <f aca="false">D46/D48-1</f>
+        <v>-0.137740870652685</v>
+      </c>
+      <c r="E50" s="15" t="n">
+        <f aca="false">E46/E48-1</f>
+        <v>-0.129547066250811</v>
+      </c>
+      <c r="F50" s="15" t="n">
+        <f aca="false">F46/F48-1</f>
+        <v>-0.121268536268651</v>
+      </c>
+      <c r="G50" s="15" t="n">
+        <f aca="false">G46/G48-1</f>
+        <v>-0.116722377510244</v>
+      </c>
+      <c r="H50" s="15" t="n">
+        <f aca="false">H46/H48-1</f>
+        <v>-0.112373658713649</v>
+      </c>
+      <c r="I50" s="15" t="n">
+        <f aca="false">I46/I48-1</f>
+        <v>-0.112578842796239</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="C52" s="17"/>
+      <c r="D52" s="17"/>
+      <c r="E52" s="17"/>
+      <c r="F52" s="17"/>
+      <c r="G52" s="17"/>
+      <c r="H52" s="17"/>
+      <c r="I52" s="17"/>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="17"/>
+      <c r="C53" s="17"/>
+      <c r="D53" s="17"/>
+      <c r="E53" s="17"/>
+      <c r="F53" s="17"/>
+      <c r="G53" s="17"/>
+      <c r="H53" s="17"/>
+      <c r="I53" s="17"/>
+    </row>
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="17"/>
+      <c r="C54" s="17"/>
+      <c r="D54" s="17"/>
+      <c r="E54" s="17"/>
+      <c r="F54" s="17"/>
+      <c r="G54" s="17"/>
+      <c r="H54" s="17"/>
+      <c r="I54" s="17"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B34:I34"/>
+    <mergeCell ref="B52:I54"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:F68"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -4025,39 +5127,39 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>183</v>
+        <v>234</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="13" t="s">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="C5" s="9" t="n">
         <v>77959624</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>186</v>
+        <v>237</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>187</v>
+        <v>238</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>1982846</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>188</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="13" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
       <c r="C7" s="10" t="n">
         <f aca="false">C5-C6</f>
@@ -4076,7 +5178,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="C9" s="8" t="n">
         <v>938.98</v>
@@ -4085,41 +5187,41 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>191</v>
+        <v>242</v>
       </c>
       <c r="C10" s="9" t="n">
         <v>5036490</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>192</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>193</v>
-      </c>
-      <c r="C11" s="21" t="n">
+        <v>244</v>
+      </c>
+      <c r="C11" s="22" t="n">
         <f aca="false">C10/C7</f>
         <v>0.0662898603044209</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>194</v>
+        <v>245</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>195</v>
+        <v>246</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>331600</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>196</v>
+        <v>247</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>197</v>
+        <v>248</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>5638571</v>
@@ -4128,7 +5230,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C14" s="11" t="n">
         <v>0.055</v>
@@ -4137,52 +5239,52 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="C15" s="10" t="n">
         <f aca="false">C13/C14</f>
         <v>102519472.727273</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>200</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>201</v>
+        <v>252</v>
       </c>
       <c r="C16" s="9" t="n">
         <v>266400</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>202</v>
+        <v>253</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>203</v>
+        <v>254</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>331776</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>204</v>
+        <v>255</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>205</v>
+        <v>256</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>294267</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>206</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>207</v>
+        <v>258</v>
       </c>
       <c r="C19" s="9" t="n">
         <v>32256</v>
@@ -4191,7 +5293,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="13" t="s">
-        <v>208</v>
+        <v>259</v>
       </c>
       <c r="C20" s="9" t="n">
         <v>152320</v>
@@ -4200,57 +5302,57 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="13" t="s">
-        <v>209</v>
+        <v>260</v>
       </c>
       <c r="C21" s="10" t="n">
         <f aca="false">SUM(C16:C20)</f>
         <v>1077019</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>210</v>
+        <v>261</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="14" t="s">
-        <v>211</v>
+        <v>262</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>212</v>
+        <v>263</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>750</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>213</v>
+        <v>264</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="s">
-        <v>214</v>
+        <v>265</v>
       </c>
       <c r="C25" s="26" t="n">
         <v>1077</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>215</v>
+        <v>266</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>216</v>
+        <v>267</v>
       </c>
       <c r="C26" s="26" t="n">
         <v>850</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>217</v>
+        <v>268</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>218</v>
+        <v>269</v>
       </c>
       <c r="C27" s="9" t="n">
         <v>126</v>
@@ -4259,7 +5361,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>219</v>
+        <v>270</v>
       </c>
       <c r="C28" s="9" t="n">
         <v>595</v>
@@ -4268,19 +5370,19 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C29" s="10" t="n">
         <f aca="false">SUM(C24:C28)</f>
         <v>3398</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="13" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="C30" s="10" t="n">
         <f aca="false">(C29-C21/C8)*C8</f>
@@ -4290,31 +5392,31 @@
     </row>
     <row r="31" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>223</v>
+        <v>274</v>
       </c>
       <c r="C31" s="11" t="n">
         <v>0.0045</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>224</v>
+        <v>275</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="13" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="C32" s="11" t="n">
         <v>0.95</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>226</v>
+        <v>277</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C33" s="21" t="n">
+        <v>278</v>
+      </c>
+      <c r="C33" s="22" t="n">
         <f aca="false">C31*C32</f>
         <v>0.004275</v>
       </c>
@@ -4322,18 +5424,18 @@
     </row>
     <row r="34" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="13" t="s">
-        <v>228</v>
+        <v>279</v>
       </c>
       <c r="C34" s="27" t="n">
         <v>0.0525</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>229</v>
+        <v>280</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="13" t="s">
-        <v>230</v>
+        <v>281</v>
       </c>
       <c r="C35" s="11" t="n">
         <v>0.05</v>
@@ -4342,36 +5444,36 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="14" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>232</v>
+        <v>283</v>
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">C10+C12+C30*0.9413</f>
         <v>5173117.5897</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>233</v>
+        <v>284</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="s">
-        <v>234</v>
+        <v>285</v>
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">C38/(C34+C33)</f>
         <v>91116117.8282695</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>235</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C40" s="10" t="n">
         <f aca="false">C39/C8</f>
@@ -4381,7 +5483,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="13" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">C33*C39</f>
@@ -4391,7 +5493,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">C41/C8</f>
@@ -4401,7 +5503,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="6" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">C38-C41</f>
@@ -4411,19 +5513,19 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>239</v>
-      </c>
-      <c r="C44" s="21" t="n">
+        <v>290</v>
+      </c>
+      <c r="C44" s="22" t="n">
         <f aca="false">C43/C7</f>
         <v>0.0629612930675232</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>240</v>
+        <v>291</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="13" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="C45" s="10" t="n">
         <f aca="false">C41</f>
@@ -4433,7 +5535,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="13" t="s">
-        <v>242</v>
+        <v>293</v>
       </c>
       <c r="C46" s="10" t="n">
         <f aca="false">C41/C8</f>
@@ -4443,19 +5545,19 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="13" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="C47" s="10" t="n">
         <f aca="false">C13+384319+C30*1.03^5*0.9413</f>
         <v>5796863.53953543</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>244</v>
+        <v>295</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="13" t="s">
-        <v>245</v>
+        <v>296</v>
       </c>
       <c r="C48" s="10" t="n">
         <f aca="false">C47/(C34+C33)</f>
@@ -4465,19 +5567,19 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C49" s="10" t="n">
         <f aca="false">C48/C8</f>
         <v>398837.484831533</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>246</v>
+        <v>297</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="13" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="C50" s="10" t="n">
         <f aca="false">C47/(C35+C33)</f>
@@ -4487,7 +5589,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C51" s="10" t="n">
         <f aca="false">C50/C8</f>
@@ -4497,12 +5599,12 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="14" t="s">
-        <v>248</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B55" s="16" t="s">
-        <v>249</v>
+        <v>300</v>
       </c>
       <c r="C55" s="16"/>
       <c r="D55" s="16"/>
@@ -4511,7 +5613,7 @@
     </row>
     <row r="56" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B56" s="16" t="s">
-        <v>250</v>
+        <v>301</v>
       </c>
       <c r="C56" s="16"/>
       <c r="D56" s="16"/>
@@ -4520,18 +5622,18 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="13" t="s">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="C57" s="9" t="n">
         <v>384319</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>252</v>
+        <v>303</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="13" t="s">
-        <v>253</v>
+        <v>304</v>
       </c>
       <c r="C58" s="10" t="n">
         <f aca="false">5825182+C57</f>
@@ -4541,19 +5643,19 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="13" t="s">
-        <v>254</v>
+        <v>305</v>
       </c>
       <c r="C59" s="10" t="n">
         <f aca="false">C58/(C34+C33)</f>
         <v>109370339.057684</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="13" t="s">
-        <v>256</v>
+        <v>307</v>
       </c>
       <c r="C60" s="10" t="n">
         <f aca="false">C33*C59</f>
@@ -4563,43 +5665,43 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C61" s="10" t="n">
         <f aca="false">C60/C8</f>
         <v>1826.39921668593</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>257</v>
+        <v>308</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="6" t="s">
-        <v>258</v>
+        <v>309</v>
       </c>
       <c r="C62" s="10" t="n">
         <f aca="false">C60-C57</f>
         <v>83239.1994715983</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>259</v>
+        <v>310</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="6" t="s">
-        <v>260</v>
+        <v>311</v>
       </c>
       <c r="C63" s="10" t="n">
         <f aca="false">C62/C34</f>
         <v>1585508.56136378</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>261</v>
+        <v>312</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C64" s="10" t="n">
         <f aca="false">C63/C8</f>
@@ -4609,7 +5711,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B66" s="16" t="s">
-        <v>262</v>
+        <v>313</v>
       </c>
       <c r="C66" s="16"/>
       <c r="D66" s="16"/>
@@ -4646,7 +5748,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -4662,22 +5764,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>263</v>
+        <v>314</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="43.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>264</v>
+        <v>315</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="14" t="s">
-        <v>184</v>
+        <v>235</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="13" t="s">
-        <v>185</v>
+        <v>236</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>41691719</v>
@@ -4695,7 +5797,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="13" t="s">
-        <v>190</v>
+        <v>241</v>
       </c>
       <c r="C8" s="8" t="n">
         <v>907.76</v>
@@ -4704,7 +5806,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="13" t="s">
-        <v>193</v>
+        <v>244</v>
       </c>
       <c r="C9" s="11" t="n">
         <v>0.0652</v>
@@ -4713,7 +5815,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="13" t="s">
-        <v>265</v>
+        <v>316</v>
       </c>
       <c r="C10" s="10" t="n">
         <f aca="false">C9*C6</f>
@@ -4723,7 +5825,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="13" t="s">
-        <v>266</v>
+        <v>317</v>
       </c>
       <c r="C11" s="9" t="n">
         <v>2914298</v>
@@ -4732,41 +5834,41 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="13" t="s">
-        <v>267</v>
+        <v>318</v>
       </c>
       <c r="C12" s="9" t="n">
         <v>356965</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>268</v>
+        <v>319</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="13" t="s">
-        <v>269</v>
+        <v>320</v>
       </c>
       <c r="C13" s="10" t="n">
         <f aca="false">C12/1.03^3</f>
         <v>326673.542431001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>270</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="13" t="s">
-        <v>271</v>
+        <v>322</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>578083</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>272</v>
+        <v>323</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="13" t="s">
-        <v>273</v>
+        <v>324</v>
       </c>
       <c r="C15" s="9" t="n">
         <v>3075765</v>
@@ -4775,7 +5877,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="13" t="s">
-        <v>198</v>
+        <v>249</v>
       </c>
       <c r="C16" s="11" t="n">
         <v>0.0525</v>
@@ -4784,30 +5886,30 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>199</v>
+        <v>250</v>
       </c>
       <c r="C17" s="10" t="n">
         <f aca="false">C15/C16</f>
         <v>58586000</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>274</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="13" t="s">
-        <v>275</v>
+        <v>326</v>
       </c>
       <c r="C18" s="9" t="n">
         <v>2448783</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>276</v>
+        <v>327</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="13" t="s">
-        <v>277</v>
+        <v>328</v>
       </c>
       <c r="C19" s="28" t="n">
         <v>6.13</v>
@@ -4816,23 +5918,23 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="14" t="s">
-        <v>278</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>220</v>
+        <v>271</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>3000</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>279</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>222</v>
+        <v>273</v>
       </c>
       <c r="C23" s="10" t="n">
         <f aca="false">(C22-C14/C7)*C7</f>
@@ -4842,18 +5944,18 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>280</v>
+        <v>331</v>
       </c>
       <c r="C24" s="11" t="n">
         <v>0.0092</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>281</v>
+        <v>332</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="s">
-        <v>225</v>
+        <v>276</v>
       </c>
       <c r="C25" s="11" t="n">
         <v>0.95</v>
@@ -4862,9 +5964,9 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="s">
-        <v>227</v>
-      </c>
-      <c r="C26" s="21" t="n">
+        <v>278</v>
+      </c>
+      <c r="C26" s="22" t="n">
         <f aca="false">C24*C25</f>
         <v>0.00874</v>
       </c>
@@ -4872,46 +5974,46 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="s">
-        <v>282</v>
+        <v>333</v>
       </c>
       <c r="C27" s="27" t="n">
         <v>0.0525</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>283</v>
+        <v>334</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="s">
-        <v>284</v>
+        <v>335</v>
       </c>
       <c r="C28" s="26" t="n">
         <v>625000</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>285</v>
+        <v>336</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="14" t="s">
-        <v>231</v>
+        <v>282</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="s">
-        <v>286</v>
+        <v>337</v>
       </c>
       <c r="C31" s="10" t="n">
         <f aca="false">C10+C13+C23*0.9413</f>
         <v>2958295.893331</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>287</v>
+        <v>338</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="13" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="C32" s="10" t="n">
         <f aca="false">C31/(C27+C26)</f>
@@ -4921,7 +6023,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="C33" s="10" t="n">
         <f aca="false">C26*C32</f>
@@ -4931,19 +6033,19 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C34" s="10" t="n">
         <f aca="false">C33/C7</f>
         <v>2606.17063281815</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>290</v>
+        <v>341</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="6" t="s">
-        <v>238</v>
+        <v>289</v>
       </c>
       <c r="C35" s="10" t="n">
         <f aca="false">C31-C33</f>
@@ -4953,31 +6055,31 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="C36" s="21" t="n">
+        <v>342</v>
+      </c>
+      <c r="C36" s="22" t="n">
         <f aca="false">C35/C6</f>
         <v>0.0608297357759334</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>292</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="13" t="s">
-        <v>243</v>
+        <v>294</v>
       </c>
       <c r="C37" s="10" t="n">
         <f aca="false">C15+367674+C23*1.03*0.9413</f>
         <v>3354160.940263</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>293</v>
+        <v>344</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="13" t="s">
-        <v>294</v>
+        <v>345</v>
       </c>
       <c r="C38" s="10" t="n">
         <f aca="false">C37/(C27+C26)</f>
@@ -4987,24 +6089,24 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="13" t="s">
-        <v>236</v>
+        <v>287</v>
       </c>
       <c r="C39" s="10" t="n">
         <f aca="false">C38/C7</f>
         <v>338091.070576703</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>295</v>
+        <v>346</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="14" t="s">
-        <v>296</v>
+        <v>347</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="13" t="s">
-        <v>297</v>
+        <v>348</v>
       </c>
       <c r="C41" s="10" t="n">
         <f aca="false">C28*C19</f>
@@ -5014,7 +6116,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="13" t="s">
-        <v>298</v>
+        <v>349</v>
       </c>
       <c r="C42" s="10" t="n">
         <f aca="false">C41-C18</f>
@@ -5024,7 +6126,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="13" t="s">
-        <v>299</v>
+        <v>350</v>
       </c>
       <c r="C43" s="10" t="n">
         <f aca="false">C6+C42</f>
@@ -5034,534 +6136,14 @@
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="C44" s="21" t="n">
+        <v>351</v>
+      </c>
+      <c r="C44" s="22" t="n">
         <f aca="false">C35/C43</f>
         <v>0.0588774039935301</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>301</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:J33"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>302</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="14" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="29" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C7" s="30" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="D7" s="30" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="30" t="n">
-        <v>0.025</v>
-      </c>
-      <c r="G7" s="30" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="30" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="C8" s="21" t="n">
-        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
-        <v>0.0635896622600766</v>
-      </c>
-      <c r="D8" s="21" t="n">
-        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
-        <v>0.0657104820418776</v>
-      </c>
-      <c r="E8" s="21" t="n">
-        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
-        <v>0.0678313018236787</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
-        <v>0.0699521216054797</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
-        <v>0.0720729413872807</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="30" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="C9" s="21" t="n">
-        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
-        <v>0.0612205372292843</v>
-      </c>
-      <c r="D9" s="21" t="n">
-        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
-        <v>0.063262342796317</v>
-      </c>
-      <c r="E9" s="21" t="n">
-        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
-        <v>0.0653041483633497</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
-        <v>0.0673459539303823</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
-        <v>0.069387759497415</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C10" s="21" t="n">
-        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
-        <v>0.0590216019076138</v>
-      </c>
-      <c r="D10" s="21" t="n">
-        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
-        <v>0.06099006936648</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
-        <v>0.0629585368253461</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
-        <v>0.0649270042842123</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
-        <v>0.0668954717430785</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
-        <v>0.0569751533965204</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
-        <v>0.0588753684330508</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
-        <v>0.0607755834695812</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
-        <v>0.0626757985061116</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
-        <v>0.064576013542642</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="30" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
-        <v>0.0550658617613987</v>
-      </c>
-      <c r="D12" s="21" t="n">
-        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
-        <v>0.0569023987829015</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
-        <v>0.0587389358044044</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
-        <v>0.0605754728259072</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
-        <v>0.0624120098474101</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="14" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C16" s="30" t="n">
-        <v>-0.1</v>
-      </c>
-      <c r="D16" s="30" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="E16" s="30" t="n">
-        <v>0</v>
-      </c>
-      <c r="F16" s="30" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="G16" s="30" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="11" t="n">
-        <v>0.0575</v>
-      </c>
-      <c r="C17" s="12" t="n">
-        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>1.88961378556508</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>1.97006138868746</v>
-      </c>
-      <c r="E17" s="12" t="n">
-        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.05050899180984</v>
-      </c>
-      <c r="F17" s="12" t="n">
-        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.13095659493223</v>
-      </c>
-      <c r="G17" s="12" t="n">
-        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.21140419805461</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="11" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>1.95257277931303</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.0365181043103</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.12046342930757</v>
-      </c>
-      <c r="F18" s="12" t="n">
-        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.20440875430484</v>
-      </c>
-      <c r="G18" s="12" t="n">
-        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.28835407930211</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="11" t="n">
-        <v>0.0625</v>
-      </c>
-      <c r="C19" s="12" t="n">
-        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.01553177306098</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.10297481993314</v>
-      </c>
-      <c r="E19" s="12" t="n">
-        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.19041786680529</v>
-      </c>
-      <c r="F19" s="12" t="n">
-        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.27786091367745</v>
-      </c>
-      <c r="G19" s="12" t="n">
-        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.3653039605496</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="11" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.07849076680893</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.16943153555598</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.26037230430302</v>
-      </c>
-      <c r="F20" s="12" t="n">
-        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.35131307305006</v>
-      </c>
-      <c r="G20" s="12" t="n">
-        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.4422538417971</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="11" t="n">
-        <v>0.0675</v>
-      </c>
-      <c r="C21" s="12" t="n">
-        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.14144976055689</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.23588825117881</v>
-      </c>
-      <c r="E21" s="12" t="n">
-        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.33032674180074</v>
-      </c>
-      <c r="F21" s="12" t="n">
-        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.42476523242267</v>
-      </c>
-      <c r="G21" s="12" t="n">
-        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.5192037230446</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="11" t="n">
-        <v>0.07</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.20440875430484</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.30234496680165</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.40028117929846</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.49821739179528</v>
-      </c>
-      <c r="G22" s="12" t="n">
-        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
-        <v>2.59615360429209</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="14" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="C25" s="7" t="s">
-        <v>310</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>311</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>312</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>313</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="9" t="n">
-        <v>399000</v>
-      </c>
-      <c r="C26" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
-        <v>0.062979087386613</v>
-      </c>
-      <c r="D26" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
-        <v>0.0621801538794552</v>
-      </c>
-      <c r="E26" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
-        <v>0.0614975322974521</v>
-      </c>
-      <c r="F26" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
-        <v>0.0608297357759334</v>
-      </c>
-      <c r="G26" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
-        <v>0.0600840809502929</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="9" t="n">
-        <v>500000</v>
-      </c>
-      <c r="C27" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
-        <v>0.0620617941324085</v>
-      </c>
-      <c r="D27" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
-        <v>0.0612744971278912</v>
-      </c>
-      <c r="E27" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
-        <v>0.0606018179600819</v>
-      </c>
-      <c r="F27" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
-        <v>0.059943747925081</v>
-      </c>
-      <c r="G27" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
-        <v>0.0592089535956768</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="9" t="n">
-        <v>625000</v>
-      </c>
-      <c r="C28" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
-        <v>0.0609577721143497</v>
-      </c>
-      <c r="D28" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
-        <v>0.0601844803966581</v>
-      </c>
-      <c r="E28" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
-        <v>0.0595237675701822</v>
-      </c>
-      <c r="F28" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
-        <v>0.0588774039935301</v>
-      </c>
-      <c r="G28" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
-        <v>0.0581556809768352</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="9" t="n">
-        <v>750000</v>
-      </c>
-      <c r="C29" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
-        <v>0.0598923426354408</v>
-      </c>
-      <c r="D29" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
-        <v>0.0591325666313858</v>
-      </c>
-      <c r="E29" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
-        <v>0.0584834018470709</v>
-      </c>
-      <c r="F29" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
-        <v>0.0578483355141464</v>
-      </c>
-      <c r="G29" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
-        <v>0.0571392268852633</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="9" t="n">
-        <v>850000</v>
-      </c>
-      <c r="C30" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
-        <v>0.0590664445870756</v>
-      </c>
-      <c r="D30" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
-        <v>0.0583171456739363</v>
-      </c>
-      <c r="E30" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
-        <v>0.0576769326838716</v>
-      </c>
-      <c r="F30" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
-        <v>0.0570506237316382</v>
-      </c>
-      <c r="G30" s="21" t="n">
-        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
-        <v>0.0563512935052504</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="2" t="s">
-        <v>316</v>
+        <v>352</v>
       </c>
     </row>
   </sheetData>
@@ -5580,237 +6162,511 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F27"/>
+  <dimension ref="B2:J33"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="46"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="14" t="s">
-        <v>318</v>
+        <v>353</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>354</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5" t="s">
-        <v>319</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>320</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>321</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="13" t="s">
-        <v>323</v>
-      </c>
-      <c r="C6" s="31" t="n">
-        <v>0.004053</v>
-      </c>
-      <c r="D6" s="31" t="n">
-        <v>0.002033</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="13" t="s">
-        <v>325</v>
-      </c>
-      <c r="C7" s="31" t="n">
-        <v>0.002797</v>
-      </c>
-      <c r="D7" s="31" t="n">
-        <v>0.000332</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>326</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="s">
-        <v>327</v>
-      </c>
-      <c r="C8" s="31" t="n">
-        <v>0.002209</v>
-      </c>
-      <c r="D8" s="31" t="n">
-        <v>0.002142</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="C9" s="31" t="n">
-        <v>0.009059</v>
-      </c>
-      <c r="D9" s="31" t="n">
-        <v>0.004507</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>330</v>
+      <c r="B5" s="14" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="29" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C7" s="30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="D7" s="30" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="30" t="n">
+        <v>0.025</v>
+      </c>
+      <c r="G7" s="30" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="30" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="C8" s="22" t="n">
+        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
+        <v>0.0635896622600766</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
+        <v>0.0657104820418776</v>
+      </c>
+      <c r="E8" s="22" t="n">
+        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
+        <v>0.0678313018236787</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
+        <v>0.0699521216054797</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B8)</f>
+        <v>0.0720729413872807</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
+        <v>0.0612205372292843</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
+        <v>0.063262342796317</v>
+      </c>
+      <c r="E9" s="22" t="n">
+        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
+        <v>0.0653041483633497</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
+        <v>0.0673459539303823</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B9)</f>
+        <v>0.069387759497415</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
+        <v>0.0590216019076138</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
+        <v>0.06099006936648</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
+        <v>0.0629585368253461</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
+        <v>0.0649270042842123</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B10)</f>
+        <v>0.0668954717430785</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="14" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="32" t="s">
-        <v>332</v>
-      </c>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="32"/>
-      <c r="C13" s="32"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="32"/>
-      <c r="F13" s="32"/>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="32"/>
-      <c r="C14" s="32"/>
-      <c r="D14" s="32"/>
-      <c r="E14" s="32"/>
-      <c r="F14" s="32"/>
+      <c r="B11" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C11" s="22" t="n">
+        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
+        <v>0.0569751533965204</v>
+      </c>
+      <c r="D11" s="22" t="n">
+        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
+        <v>0.0588753684330508</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
+        <v>0.0607755834695812</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
+        <v>0.0626757985061116</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B11)</f>
+        <v>0.064576013542642</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="30" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="C12" s="22" t="n">
+        <f aca="false">((6355373*(1+C$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
+        <v>0.0550658617613987</v>
+      </c>
+      <c r="D12" s="22" t="n">
+        <f aca="false">((6355373*(1+D$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
+        <v>0.0569023987829015</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <f aca="false">((6355373*(1+E$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
+        <v>0.0587389358044044</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <f aca="false">((6355373*(1+F$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
+        <v>0.0605754728259072</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <f aca="false">((6355373*(1+G$7)+4_Emblem_Norm!$C$29*256)*0.9413-(1959830-331600)-4_Emblem_Norm!$C$41)/(4_Emblem_Norm!$C$7+54579077*$B12)</f>
+        <v>0.0624120098474101</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="14" t="s">
+        <v>358</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="14" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="13" t="s">
-        <v>334</v>
-      </c>
-      <c r="C17" s="10" t="n">
-        <f aca="false">3428-1340</f>
-        <v>2088</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>335</v>
+      <c r="C16" s="30" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="D16" s="30" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E16" s="30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" s="30" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G16" s="30" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="11" t="n">
+        <v>0.0575</v>
+      </c>
+      <c r="C17" s="12" t="n">
+        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>1.88961378556508</v>
+      </c>
+      <c r="D17" s="12" t="n">
+        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>1.97006138868746</v>
+      </c>
+      <c r="E17" s="12" t="n">
+        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.05050899180984</v>
+      </c>
+      <c r="F17" s="12" t="n">
+        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.13095659493223</v>
+      </c>
+      <c r="G17" s="12" t="n">
+        <f aca="false">(($B17*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.21140419805461</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>359</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="13" t="s">
-        <v>336</v>
-      </c>
-      <c r="C18" s="10" t="n">
-        <f aca="false">C17/0.05</f>
-        <v>41760</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>337</v>
+      <c r="B18" s="11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C18" s="12" t="n">
+        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>1.95257277931303</v>
+      </c>
+      <c r="D18" s="12" t="n">
+        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.0365181043103</v>
+      </c>
+      <c r="E18" s="12" t="n">
+        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.12046342930757</v>
+      </c>
+      <c r="F18" s="12" t="n">
+        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.20440875430484</v>
+      </c>
+      <c r="G18" s="12" t="n">
+        <f aca="false">(($B18*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.28835407930211</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="s">
-        <v>338</v>
-      </c>
-      <c r="C19" s="9" t="n">
-        <v>381944</v>
-      </c>
-      <c r="F19" s="2"/>
+      <c r="B19" s="11" t="n">
+        <v>0.0625</v>
+      </c>
+      <c r="C19" s="12" t="n">
+        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.01553177306098</v>
+      </c>
+      <c r="D19" s="12" t="n">
+        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.10297481993314</v>
+      </c>
+      <c r="E19" s="12" t="n">
+        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.19041786680529</v>
+      </c>
+      <c r="F19" s="12" t="n">
+        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.27786091367745</v>
+      </c>
+      <c r="G19" s="12" t="n">
+        <f aca="false">(($B19*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.3653039605496</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="s">
-        <v>339</v>
-      </c>
-      <c r="C20" s="10" t="n">
-        <f aca="false">5027967+C17*288</f>
-        <v>5629311</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>340</v>
+      <c r="B20" s="11" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="C20" s="12" t="n">
+        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.07849076680893</v>
+      </c>
+      <c r="D20" s="12" t="n">
+        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.16943153555598</v>
+      </c>
+      <c r="E20" s="12" t="n">
+        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.26037230430302</v>
+      </c>
+      <c r="F20" s="12" t="n">
+        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.35131307305006</v>
+      </c>
+      <c r="G20" s="12" t="n">
+        <f aca="false">(($B20*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.4422538417971</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="13" t="s">
-        <v>341</v>
-      </c>
-      <c r="C21" s="10" t="n">
-        <f aca="false">C20/0.045709/288</f>
-        <v>427622.979063204</v>
-      </c>
-      <c r="F21" s="2"/>
+      <c r="B21" s="11" t="n">
+        <v>0.0675</v>
+      </c>
+      <c r="C21" s="12" t="n">
+        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.14144976055689</v>
+      </c>
+      <c r="D21" s="12" t="n">
+        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.23588825117881</v>
+      </c>
+      <c r="E21" s="12" t="n">
+        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.33032674180074</v>
+      </c>
+      <c r="F21" s="12" t="n">
+        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.42476523242267</v>
+      </c>
+      <c r="G21" s="12" t="n">
+        <f aca="false">(($B21*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.5192037230446</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="13" t="s">
-        <v>342</v>
-      </c>
-      <c r="C22" s="9" t="n">
-        <v>327778</v>
-      </c>
-      <c r="F22" s="2"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="s">
-        <v>343</v>
-      </c>
-      <c r="C23" s="15" t="n">
-        <f aca="false">C22/C21-1</f>
-        <v>-0.233488338914656</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>344</v>
+      <c r="B22" s="11" t="n">
+        <v>0.07</v>
+      </c>
+      <c r="C22" s="12" t="n">
+        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+C$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.20440875430484</v>
+      </c>
+      <c r="D22" s="12" t="n">
+        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+D$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.30234496680165</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+E$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.40028117929846</v>
+      </c>
+      <c r="F22" s="12" t="n">
+        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+F$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.49821739179528</v>
+      </c>
+      <c r="G22" s="12" t="n">
+        <f aca="false">(($B22*4_Emblem_Norm!$C$7*(1+G$16)+(1959830-331600)+4_Emblem_Norm!$C$41)/0.9413-4_Emblem_Norm!$C$29*256)/256/12/938.98</f>
+        <v>2.59615360429209</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="13" t="s">
-        <v>345</v>
-      </c>
-      <c r="C24" s="10" t="n">
-        <f aca="false">(5904654-C17*360)/0.05/360</f>
-        <v>286276.333333333</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="16" t="s">
-        <v>347</v>
-      </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16"/>
+      <c r="B24" s="14" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C25" s="7" t="s">
+        <v>361</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>362</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>363</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>364</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="9" t="n">
+        <v>399000</v>
+      </c>
+      <c r="C26" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
+        <v>0.062979087386613</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
+        <v>0.0621801538794552</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
+        <v>0.0614975322974521</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
+        <v>0.0608297357759334</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B26*6.13-2448783))</f>
+        <v>0.0600840809502929</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>366</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="16"/>
-      <c r="C27" s="16"/>
-      <c r="D27" s="16"/>
-      <c r="E27" s="16"/>
-      <c r="F27" s="16"/>
+      <c r="B27" s="9" t="n">
+        <v>500000</v>
+      </c>
+      <c r="C27" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
+        <v>0.0620617941324085</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
+        <v>0.0612744971278912</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
+        <v>0.0606018179600819</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
+        <v>0.059943747925081</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B27*6.13-2448783))</f>
+        <v>0.0592089535956768</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="9" t="n">
+        <v>625000</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
+        <v>0.0609577721143497</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
+        <v>0.0601844803966581</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
+        <v>0.0595237675701822</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
+        <v>0.0588774039935301</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B28*6.13-2448783))</f>
+        <v>0.0581556809768352</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="9" t="n">
+        <v>750000</v>
+      </c>
+      <c r="C29" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
+        <v>0.0598923426354408</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
+        <v>0.0591325666313858</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
+        <v>0.0584834018470709</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
+        <v>0.0578483355141464</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B29*6.13-2448783))</f>
+        <v>0.0571392268852633</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="9" t="n">
+        <v>850000</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.007*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.007*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
+        <v>0.0590664445870756</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0078*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0078*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
+        <v>0.0583171456739363</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0085*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0085*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
+        <v>0.0576769326838716</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.0092*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.0092*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
+        <v>0.0570506237316382</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <f aca="false">(5_Judy_Norm!$C$31-(0.01*0.95)*(5_Judy_Norm!$C$31/(5_Judy_Norm!$C$27+0.01*0.95)))/(5_Judy_Norm!$C$6+MAX(0,$B30*6.13-2448783))</f>
+        <v>0.0563512935052504</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="2" t="s">
+        <v>367</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B12:F14"/>
-    <mergeCell ref="B26:F27"/>
-  </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -5826,311 +6682,236 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:F39"/>
+  <dimension ref="B2:F27"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="54"/>
   </cols>
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="14" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="5"/>
+        <v>369</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>370</v>
+      </c>
       <c r="C5" s="5" t="s">
-        <v>20</v>
+        <v>371</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>1130</v>
-      </c>
-      <c r="D6" s="8" t="n">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>228</v>
-      </c>
-      <c r="D7" s="8" t="n">
-        <v>44</v>
+        <v>372</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="13" t="s">
+        <v>374</v>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>0.004053</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>0.002033</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="13" t="s">
+        <v>376</v>
+      </c>
+      <c r="C7" s="31" t="n">
+        <v>0.002797</v>
+      </c>
+      <c r="D7" s="31" t="n">
+        <v>0.000332</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>377</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>507</v>
-      </c>
-      <c r="D8" s="8" t="n">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>0.002209</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>0.002142</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="53.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>309</v>
-      </c>
-      <c r="D9" s="8" t="n">
-        <v>40</v>
+        <v>380</v>
+      </c>
+      <c r="C9" s="31" t="n">
+        <v>0.009059</v>
+      </c>
+      <c r="D9" s="31" t="n">
+        <v>0.004507</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="14" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>356</v>
-      </c>
+        <v>382</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B12" s="32" t="s">
+        <v>383</v>
+      </c>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="s">
-        <v>357</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>552</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>358</v>
-      </c>
+      <c r="B13" s="32"/>
+      <c r="C13" s="32"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="32"/>
+      <c r="F13" s="32"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="13" t="s">
-        <v>359</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>213</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="13" t="s">
-        <v>360</v>
-      </c>
-      <c r="C15" s="8" t="n">
-        <v>212</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>361</v>
-      </c>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="s">
-        <v>362</v>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>164</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>363</v>
+      <c r="B16" s="14" t="s">
+        <v>384</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="13" t="s">
-        <v>364</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>72</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>361</v>
+        <v>385</v>
+      </c>
+      <c r="C17" s="10" t="n">
+        <f aca="false">3428-1340</f>
+        <v>2088</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>386</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="17" t="s">
-        <v>365</v>
-      </c>
-      <c r="C18" s="33" t="n">
-        <f aca="false">SUM(C13:C17)</f>
-        <v>1213</v>
-      </c>
+      <c r="B18" s="13" t="s">
+        <v>387</v>
+      </c>
+      <c r="C18" s="10" t="n">
+        <f aca="false">C17/0.05</f>
+        <v>41760</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="13" t="s">
+        <v>389</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>381944</v>
+      </c>
+      <c r="F19" s="2"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="14" t="s">
-        <v>366</v>
+      <c r="B20" s="13" t="s">
+        <v>390</v>
+      </c>
+      <c r="C20" s="10" t="n">
+        <f aca="false">5027967+C17*288</f>
+        <v>5629311</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>391</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>355</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>43</v>
-      </c>
+      <c r="B21" s="13" t="s">
+        <v>392</v>
+      </c>
+      <c r="C21" s="10" t="n">
+        <f aca="false">C20/0.045709/288</f>
+        <v>427622.979063204</v>
+      </c>
+      <c r="F21" s="2"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="13" t="s">
-        <v>367</v>
-      </c>
-      <c r="C22" s="8" t="n">
-        <v>472</v>
-      </c>
+        <v>393</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>327778</v>
+      </c>
+      <c r="F22" s="2"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="13" t="s">
-        <v>368</v>
-      </c>
-      <c r="C23" s="8" t="n">
-        <v>390</v>
+        <v>394</v>
+      </c>
+      <c r="C23" s="15" t="n">
+        <f aca="false">C22/C21-1</f>
+        <v>-0.233488338914656</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>395</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="13" t="s">
-        <v>369</v>
-      </c>
-      <c r="C24" s="8" t="n">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="13" t="s">
-        <v>370</v>
-      </c>
-      <c r="C25" s="8" t="n">
-        <v>301</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="s">
-        <v>371</v>
-      </c>
-      <c r="C26" s="8" t="n">
-        <v>275</v>
-      </c>
+        <v>396</v>
+      </c>
+      <c r="C24" s="10" t="n">
+        <f aca="false">(5904654-C17*360)/0.05/360</f>
+        <v>286276.333333333</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B26" s="16" t="s">
+        <v>398</v>
+      </c>
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="s">
-        <v>372</v>
-      </c>
-      <c r="C27" s="8" t="n">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="13" t="s">
-        <v>373</v>
-      </c>
-      <c r="C28" s="8" t="n">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="13" t="s">
-        <v>374</v>
-      </c>
-      <c r="C29" s="8" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="s">
-        <v>375</v>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="13" t="s">
-        <v>376</v>
-      </c>
-      <c r="C31" s="8" t="n">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="13" t="s">
-        <v>377</v>
-      </c>
-      <c r="C32" s="8" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="13" t="s">
-        <v>378</v>
-      </c>
-      <c r="C33" s="8" t="n">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="13" t="s">
-        <v>379</v>
-      </c>
-      <c r="C34" s="8" t="n">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="6" t="s">
-        <v>380</v>
-      </c>
-      <c r="C35" s="8" t="n">
-        <v>256</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="17" t="s">
-        <v>381</v>
-      </c>
-      <c r="C36" s="33" t="n">
-        <f aca="false">SUM(C22:C35)</f>
-        <v>3428</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="16" t="s">
-        <v>382</v>
-      </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="D39" s="16"/>
-      <c r="E39" s="16"/>
-      <c r="F39" s="16"/>
+      <c r="B27" s="16"/>
+      <c r="C27" s="16"/>
+      <c r="D27" s="16"/>
+      <c r="E27" s="16"/>
+      <c r="F27" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B38:F39"/>
+  <mergeCells count="2">
+    <mergeCell ref="B12:F14"/>
+    <mergeCell ref="B26:F27"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
